--- a/templates/ERC000049/metadata_template_ERC000049.xlsx
+++ b/templates/ERC000049/metadata_template_ERC000049.xlsx
@@ -19,14 +19,14 @@
   <definedNames>
     <definedName name="detectiontype">'cv_sample'!$AG$1:$AG$2</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AY$1:$AY$289</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AY$1:$AY$294</definedName>
     <definedName name="hostpredictionapproach">'cv_sample'!$BB$1:$BB$7</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="observedbioticrelationship">'cv_sample'!$G$1:$G$5</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="predictedgenomestructure">'cv_sample'!$AF$1:$AF$3</definedName>
     <definedName name="predictedgenometype">'cv_sample'!$AE$1:$AE$10</definedName>
     <definedName name="reassemblypostbinning">'cv_sample'!$Z$1:$Z$2</definedName>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="771">
   <si>
     <t>alias</t>
   </si>
@@ -459,6 +459,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -549,6 +552,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1224,7 +1230,7 @@
     <t>amount or size of sample collected</t>
   </si>
   <si>
-    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: m3)</t>
+    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: kg)</t>
   </si>
   <si>
     <t>size fraction selected</t>
@@ -1446,9 +1452,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1467,6 +1470,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1668,6 +1674,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1677,9 +1686,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1719,7 +1725,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1788,6 +1794,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1863,6 +1872,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1884,6 +1896,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1929,6 +1944,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1941,6 +1959,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1950,9 +1971,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1977,6 +1995,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2037,12 +2058,12 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
   </si>
   <si>
-    <t>Wake Island</t>
-  </si>
-  <si>
     <t>Wallis and Futuna</t>
   </si>
   <si>
@@ -2334,7 +2355,7 @@
     <t>depth</t>
   </si>
   <si>
-    <t>(Optional) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: mm)</t>
+    <t>(Optional) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: m)</t>
   </si>
 </sst>
 </file>
@@ -2861,10 +2882,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2905,10 +2926,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2935,7 +2956,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -2952,7 +2973,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -2969,7 +2990,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -2986,7 +3007,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -3003,7 +3024,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -3020,7 +3041,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -3037,7 +3058,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -3054,7 +3075,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -3071,7 +3092,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -3088,7 +3109,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -3102,7 +3123,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -3116,7 +3137,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -3130,7 +3151,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -3144,7 +3165,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -3158,7 +3179,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -3172,7 +3193,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -3186,7 +3207,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -3200,7 +3221,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -3210,8 +3231,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -3222,7 +3246,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -3233,7 +3257,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3244,7 +3268,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3255,7 +3279,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3266,7 +3290,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3277,7 +3301,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3288,7 +3312,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3299,7 +3323,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3310,7 +3334,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3321,7 +3345,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3332,7 +3356,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3343,7 +3367,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3354,7 +3378,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3362,7 +3386,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3370,7 +3394,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3378,7 +3402,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3386,7 +3410,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3394,7 +3418,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3402,7 +3426,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3410,7 +3434,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3418,7 +3442,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3426,7 +3450,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3434,236 +3458,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3685,27 +3714,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3725,122 +3754,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3864,456 +3893,456 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
     </row>
     <row r="2" spans="1:76" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
     </row>
   </sheetData>
@@ -4364,181 +4393,181 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:BV289"/>
+  <dimension ref="G1:BV294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:74">
       <c r="G1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Z1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AD1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AE1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AF1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AG1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AL1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AY1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="BB1" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="BI1" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="BS1" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="BU1" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="BV1" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
     </row>
     <row r="2" spans="7:74">
       <c r="G2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Z2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AD2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AE2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AF2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AG2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AY2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="BB2" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="BI2" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="BS2" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="BU2" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="BV2" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
     </row>
     <row r="3" spans="7:74">
       <c r="G3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AD3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AE3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AF3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AL3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AY3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="BB3" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="BI3" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="BU3" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="BV3" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
     </row>
     <row r="4" spans="7:74">
       <c r="G4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AD4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AE4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AY4" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="BB4" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="BI4" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="BU4" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="BV4" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
     </row>
     <row r="5" spans="7:74">
       <c r="G5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AD5" t="s">
         <v>116</v>
       </c>
       <c r="AE5" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AY5" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="BB5" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="BU5" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="BV5" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
     </row>
     <row r="6" spans="7:74">
       <c r="AD6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AE6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AY6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="BB6" t="s">
         <v>116</v>
@@ -4547,49 +4576,49 @@
         <v>116</v>
       </c>
       <c r="BV6" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
     </row>
     <row r="7" spans="7:74">
       <c r="AD7" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AE7" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AY7" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="BB7" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="BV7" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
     </row>
     <row r="8" spans="7:74">
       <c r="AD8" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AE8" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AY8" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="BV8" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
     </row>
     <row r="9" spans="7:74">
       <c r="AD9" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AE9" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AY9" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="BV9" t="s">
         <v>116</v>
@@ -4597,1417 +4626,1442 @@
     </row>
     <row r="10" spans="7:74">
       <c r="AD10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AE10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AY10" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="BV10" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
     </row>
     <row r="11" spans="7:74">
       <c r="AY11" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="BV11" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
     </row>
     <row r="12" spans="7:74">
       <c r="AY12" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="BV12" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
     </row>
     <row r="13" spans="7:74">
       <c r="AY13" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="14" spans="7:74">
       <c r="AY14" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="15" spans="7:74">
       <c r="AY15" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="16" spans="7:74">
       <c r="AY16" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="17" spans="51:51">
       <c r="AY17" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="18" spans="51:51">
       <c r="AY18" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="19" spans="51:51">
       <c r="AY19" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="20" spans="51:51">
       <c r="AY20" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="21" spans="51:51">
       <c r="AY21" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="22" spans="51:51">
       <c r="AY22" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="23" spans="51:51">
       <c r="AY23" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="24" spans="51:51">
       <c r="AY24" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="25" spans="51:51">
       <c r="AY25" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="26" spans="51:51">
       <c r="AY26" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="27" spans="51:51">
       <c r="AY27" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="28" spans="51:51">
       <c r="AY28" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="29" spans="51:51">
       <c r="AY29" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="30" spans="51:51">
       <c r="AY30" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="31" spans="51:51">
       <c r="AY31" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="32" spans="51:51">
       <c r="AY32" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="33" spans="51:51">
       <c r="AY33" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="34" spans="51:51">
       <c r="AY34" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="35" spans="51:51">
       <c r="AY35" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="36" spans="51:51">
       <c r="AY36" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="37" spans="51:51">
       <c r="AY37" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="38" spans="51:51">
       <c r="AY38" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="39" spans="51:51">
       <c r="AY39" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="40" spans="51:51">
       <c r="AY40" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="41" spans="51:51">
       <c r="AY41" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="42" spans="51:51">
       <c r="AY42" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="43" spans="51:51">
       <c r="AY43" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="44" spans="51:51">
       <c r="AY44" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="45" spans="51:51">
       <c r="AY45" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="46" spans="51:51">
       <c r="AY46" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="47" spans="51:51">
       <c r="AY47" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="48" spans="51:51">
       <c r="AY48" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="49" spans="51:51">
       <c r="AY49" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="50" spans="51:51">
       <c r="AY50" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="51" spans="51:51">
       <c r="AY51" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="52" spans="51:51">
       <c r="AY52" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="53" spans="51:51">
       <c r="AY53" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="54" spans="51:51">
       <c r="AY54" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="55" spans="51:51">
       <c r="AY55" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="56" spans="51:51">
       <c r="AY56" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="57" spans="51:51">
       <c r="AY57" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="58" spans="51:51">
       <c r="AY58" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="59" spans="51:51">
       <c r="AY59" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="60" spans="51:51">
       <c r="AY60" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="61" spans="51:51">
       <c r="AY61" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="62" spans="51:51">
       <c r="AY62" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="63" spans="51:51">
       <c r="AY63" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="64" spans="51:51">
       <c r="AY64" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="65" spans="51:51">
       <c r="AY65" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="66" spans="51:51">
       <c r="AY66" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="67" spans="51:51">
       <c r="AY67" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="68" spans="51:51">
       <c r="AY68" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="69" spans="51:51">
       <c r="AY69" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="70" spans="51:51">
       <c r="AY70" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="71" spans="51:51">
       <c r="AY71" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="72" spans="51:51">
       <c r="AY72" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="73" spans="51:51">
       <c r="AY73" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="74" spans="51:51">
       <c r="AY74" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="75" spans="51:51">
       <c r="AY75" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="76" spans="51:51">
       <c r="AY76" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="77" spans="51:51">
       <c r="AY77" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="78" spans="51:51">
       <c r="AY78" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="79" spans="51:51">
       <c r="AY79" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="80" spans="51:51">
       <c r="AY80" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="81" spans="51:51">
       <c r="AY81" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="82" spans="51:51">
       <c r="AY82" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="83" spans="51:51">
       <c r="AY83" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="84" spans="51:51">
       <c r="AY84" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="85" spans="51:51">
       <c r="AY85" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="86" spans="51:51">
       <c r="AY86" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="87" spans="51:51">
       <c r="AY87" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="88" spans="51:51">
       <c r="AY88" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="89" spans="51:51">
       <c r="AY89" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="90" spans="51:51">
       <c r="AY90" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="91" spans="51:51">
       <c r="AY91" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="92" spans="51:51">
       <c r="AY92" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="93" spans="51:51">
       <c r="AY93" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="94" spans="51:51">
       <c r="AY94" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="95" spans="51:51">
       <c r="AY95" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="96" spans="51:51">
       <c r="AY96" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="97" spans="51:51">
       <c r="AY97" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="98" spans="51:51">
       <c r="AY98" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="99" spans="51:51">
       <c r="AY99" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="100" spans="51:51">
       <c r="AY100" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="101" spans="51:51">
       <c r="AY101" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="102" spans="51:51">
       <c r="AY102" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="103" spans="51:51">
       <c r="AY103" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="104" spans="51:51">
       <c r="AY104" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="105" spans="51:51">
       <c r="AY105" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="106" spans="51:51">
       <c r="AY106" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="107" spans="51:51">
       <c r="AY107" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="108" spans="51:51">
       <c r="AY108" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="109" spans="51:51">
       <c r="AY109" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="110" spans="51:51">
       <c r="AY110" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="111" spans="51:51">
       <c r="AY111" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="112" spans="51:51">
       <c r="AY112" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="113" spans="51:51">
       <c r="AY113" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="114" spans="51:51">
       <c r="AY114" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="115" spans="51:51">
       <c r="AY115" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="116" spans="51:51">
       <c r="AY116" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="117" spans="51:51">
       <c r="AY117" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="118" spans="51:51">
       <c r="AY118" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="119" spans="51:51">
       <c r="AY119" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="120" spans="51:51">
       <c r="AY120" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="121" spans="51:51">
       <c r="AY121" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="122" spans="51:51">
       <c r="AY122" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="123" spans="51:51">
       <c r="AY123" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="124" spans="51:51">
       <c r="AY124" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="125" spans="51:51">
       <c r="AY125" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="126" spans="51:51">
       <c r="AY126" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="127" spans="51:51">
       <c r="AY127" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="128" spans="51:51">
       <c r="AY128" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="129" spans="51:51">
       <c r="AY129" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="130" spans="51:51">
       <c r="AY130" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="131" spans="51:51">
       <c r="AY131" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="132" spans="51:51">
       <c r="AY132" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="133" spans="51:51">
       <c r="AY133" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="134" spans="51:51">
       <c r="AY134" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="135" spans="51:51">
       <c r="AY135" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="136" spans="51:51">
       <c r="AY136" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="137" spans="51:51">
       <c r="AY137" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="138" spans="51:51">
       <c r="AY138" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="139" spans="51:51">
       <c r="AY139" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="140" spans="51:51">
       <c r="AY140" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="141" spans="51:51">
       <c r="AY141" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="142" spans="51:51">
       <c r="AY142" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="143" spans="51:51">
       <c r="AY143" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="144" spans="51:51">
       <c r="AY144" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="145" spans="51:51">
       <c r="AY145" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="146" spans="51:51">
       <c r="AY146" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="147" spans="51:51">
       <c r="AY147" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="148" spans="51:51">
       <c r="AY148" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="149" spans="51:51">
       <c r="AY149" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="150" spans="51:51">
       <c r="AY150" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="151" spans="51:51">
       <c r="AY151" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="152" spans="51:51">
       <c r="AY152" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="153" spans="51:51">
       <c r="AY153" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="154" spans="51:51">
       <c r="AY154" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="155" spans="51:51">
       <c r="AY155" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="156" spans="51:51">
       <c r="AY156" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="157" spans="51:51">
       <c r="AY157" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="158" spans="51:51">
       <c r="AY158" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="159" spans="51:51">
       <c r="AY159" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="160" spans="51:51">
       <c r="AY160" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="161" spans="51:51">
       <c r="AY161" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="162" spans="51:51">
       <c r="AY162" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="163" spans="51:51">
       <c r="AY163" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="164" spans="51:51">
       <c r="AY164" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="165" spans="51:51">
       <c r="AY165" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="166" spans="51:51">
       <c r="AY166" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="167" spans="51:51">
       <c r="AY167" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="168" spans="51:51">
       <c r="AY168" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="169" spans="51:51">
       <c r="AY169" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="170" spans="51:51">
       <c r="AY170" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="171" spans="51:51">
       <c r="AY171" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="172" spans="51:51">
       <c r="AY172" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="173" spans="51:51">
       <c r="AY173" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="174" spans="51:51">
       <c r="AY174" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="175" spans="51:51">
       <c r="AY175" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="176" spans="51:51">
       <c r="AY176" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="177" spans="51:51">
       <c r="AY177" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="178" spans="51:51">
       <c r="AY178" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="179" spans="51:51">
       <c r="AY179" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="180" spans="51:51">
       <c r="AY180" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="181" spans="51:51">
       <c r="AY181" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="182" spans="51:51">
       <c r="AY182" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="183" spans="51:51">
       <c r="AY183" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="184" spans="51:51">
       <c r="AY184" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="185" spans="51:51">
       <c r="AY185" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="186" spans="51:51">
       <c r="AY186" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="187" spans="51:51">
       <c r="AY187" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="188" spans="51:51">
       <c r="AY188" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="189" spans="51:51">
       <c r="AY189" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="190" spans="51:51">
       <c r="AY190" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="191" spans="51:51">
       <c r="AY191" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="192" spans="51:51">
       <c r="AY192" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="193" spans="51:51">
       <c r="AY193" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="194" spans="51:51">
       <c r="AY194" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="195" spans="51:51">
       <c r="AY195" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="196" spans="51:51">
       <c r="AY196" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="197" spans="51:51">
       <c r="AY197" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="198" spans="51:51">
       <c r="AY198" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="199" spans="51:51">
       <c r="AY199" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="200" spans="51:51">
       <c r="AY200" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="201" spans="51:51">
       <c r="AY201" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="202" spans="51:51">
       <c r="AY202" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="203" spans="51:51">
       <c r="AY203" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="204" spans="51:51">
       <c r="AY204" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="205" spans="51:51">
       <c r="AY205" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="206" spans="51:51">
       <c r="AY206" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="207" spans="51:51">
       <c r="AY207" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="208" spans="51:51">
       <c r="AY208" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="209" spans="51:51">
       <c r="AY209" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="210" spans="51:51">
       <c r="AY210" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="211" spans="51:51">
       <c r="AY211" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="212" spans="51:51">
       <c r="AY212" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="213" spans="51:51">
       <c r="AY213" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="214" spans="51:51">
       <c r="AY214" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="215" spans="51:51">
       <c r="AY215" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="216" spans="51:51">
       <c r="AY216" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="217" spans="51:51">
       <c r="AY217" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="218" spans="51:51">
       <c r="AY218" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="219" spans="51:51">
       <c r="AY219" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="220" spans="51:51">
       <c r="AY220" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="221" spans="51:51">
       <c r="AY221" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="222" spans="51:51">
       <c r="AY222" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="223" spans="51:51">
       <c r="AY223" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="224" spans="51:51">
       <c r="AY224" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="225" spans="51:51">
       <c r="AY225" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="226" spans="51:51">
       <c r="AY226" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="227" spans="51:51">
       <c r="AY227" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="228" spans="51:51">
       <c r="AY228" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="229" spans="51:51">
       <c r="AY229" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="230" spans="51:51">
       <c r="AY230" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="231" spans="51:51">
       <c r="AY231" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="232" spans="51:51">
       <c r="AY232" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="233" spans="51:51">
       <c r="AY233" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="234" spans="51:51">
       <c r="AY234" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="235" spans="51:51">
       <c r="AY235" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="236" spans="51:51">
       <c r="AY236" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="237" spans="51:51">
       <c r="AY237" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="238" spans="51:51">
       <c r="AY238" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="239" spans="51:51">
       <c r="AY239" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="240" spans="51:51">
       <c r="AY240" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="241" spans="51:51">
       <c r="AY241" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="242" spans="51:51">
       <c r="AY242" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="243" spans="51:51">
       <c r="AY243" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="244" spans="51:51">
       <c r="AY244" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="245" spans="51:51">
       <c r="AY245" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="246" spans="51:51">
       <c r="AY246" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="247" spans="51:51">
       <c r="AY247" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="248" spans="51:51">
       <c r="AY248" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="249" spans="51:51">
       <c r="AY249" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="250" spans="51:51">
       <c r="AY250" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="251" spans="51:51">
       <c r="AY251" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="252" spans="51:51">
       <c r="AY252" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="253" spans="51:51">
       <c r="AY253" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="254" spans="51:51">
       <c r="AY254" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="255" spans="51:51">
       <c r="AY255" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="256" spans="51:51">
       <c r="AY256" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="257" spans="51:51">
       <c r="AY257" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="258" spans="51:51">
       <c r="AY258" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="259" spans="51:51">
       <c r="AY259" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="260" spans="51:51">
       <c r="AY260" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="261" spans="51:51">
       <c r="AY261" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="262" spans="51:51">
       <c r="AY262" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="263" spans="51:51">
       <c r="AY263" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="264" spans="51:51">
       <c r="AY264" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="265" spans="51:51">
       <c r="AY265" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="266" spans="51:51">
       <c r="AY266" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="267" spans="51:51">
       <c r="AY267" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="268" spans="51:51">
       <c r="AY268" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="269" spans="51:51">
       <c r="AY269" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="270" spans="51:51">
       <c r="AY270" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="271" spans="51:51">
       <c r="AY271" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="272" spans="51:51">
       <c r="AY272" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="273" spans="51:51">
       <c r="AY273" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="274" spans="51:51">
       <c r="AY274" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="275" spans="51:51">
       <c r="AY275" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="276" spans="51:51">
       <c r="AY276" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="277" spans="51:51">
       <c r="AY277" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="278" spans="51:51">
       <c r="AY278" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="279" spans="51:51">
       <c r="AY279" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="280" spans="51:51">
       <c r="AY280" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="281" spans="51:51">
       <c r="AY281" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="282" spans="51:51">
       <c r="AY282" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="283" spans="51:51">
       <c r="AY283" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="284" spans="51:51">
       <c r="AY284" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="285" spans="51:51">
       <c r="AY285" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="286" spans="51:51">
       <c r="AY286" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="287" spans="51:51">
       <c r="AY287" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="288" spans="51:51">
       <c r="AY288" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="289" spans="51:51">
       <c r="AY289" t="s">
-        <v>684</v>
+        <v>686</v>
+      </c>
+    </row>
+    <row r="290" spans="51:51">
+      <c r="AY290" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="291" spans="51:51">
+      <c r="AY291" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="292" spans="51:51">
+      <c r="AY292" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="293" spans="51:51">
+      <c r="AY293" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="294" spans="51:51">
+      <c r="AY294" t="s">
+        <v>691</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000049/metadata_template_ERC000049.xlsx
+++ b/templates/ERC000049/metadata_template_ERC000049.xlsx
@@ -17,33 +17,33 @@
     <sheet name="cv_sample" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="detectiontype">'cv_sample'!$AE$1:$AE$2</definedName>
+    <definedName name="detectiontype">'cv_sample'!$AF$1:$AF$2</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AW$1:$AW$289</definedName>
-    <definedName name="hostpredictionapproach">'cv_sample'!$AZ$1:$AZ$7</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AX$1:$AX$294</definedName>
+    <definedName name="hostpredictionapproach">'cv_sample'!$BA$1:$BA$7</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="observedbioticrelationship">'cv_sample'!$E$1:$E$5</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
-    <definedName name="predictedgenomestructure">'cv_sample'!$AD$1:$AD$3</definedName>
-    <definedName name="predictedgenometype">'cv_sample'!$AC$1:$AC$10</definedName>
-    <definedName name="reassemblypostbinning">'cv_sample'!$X$1:$X$2</definedName>
-    <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$BG$1:$BG$4</definedName>
-    <definedName name="sortingtechnology">'cv_sample'!$BS$1:$BS$6</definedName>
-    <definedName name="sourceofUViGs">'cv_sample'!$AB$1:$AB$10</definedName>
+    <definedName name="observedbioticrelationship">'cv_sample'!$F$1:$F$5</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
+    <definedName name="predictedgenomestructure">'cv_sample'!$AE$1:$AE$3</definedName>
+    <definedName name="predictedgenometype">'cv_sample'!$AD$1:$AD$10</definedName>
+    <definedName name="reassemblypostbinning">'cv_sample'!$Y$1:$Y$2</definedName>
+    <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$BH$1:$BH$4</definedName>
+    <definedName name="sortingtechnology">'cv_sample'!$BT$1:$BT$6</definedName>
+    <definedName name="sourceofUViGs">'cv_sample'!$AC$1:$AC$10</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="UViGassemblyquality">'cv_sample'!$AJ$1:$AJ$3</definedName>
-    <definedName name="virusenrichmentapproach">'cv_sample'!$BT$1:$BT$12</definedName>
-    <definedName name="WGAamplificationapproach">'cv_sample'!$BQ$1:$BQ$2</definedName>
+    <definedName name="UViGassemblyquality">'cv_sample'!$AK$1:$AK$3</definedName>
+    <definedName name="virusenrichmentapproach">'cv_sample'!$BU$1:$BU$12</definedName>
+    <definedName name="WGAamplificationapproach">'cv_sample'!$BR$1:$BR$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="769">
   <si>
     <t>alias</t>
   </si>
@@ -459,6 +459,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -549,6 +552,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -849,6 +855,12 @@
     <t>(Mandatory) Ncbi taxonomy identifier.  this is appropriate for individual organisms and some environmental samples.</t>
   </si>
   <si>
+    <t>scientific_name</t>
+  </si>
+  <si>
+    <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
     <t>sample_description</t>
   </si>
   <si>
@@ -1434,9 +1446,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1455,6 +1464,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1656,6 +1668,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1665,9 +1680,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1707,7 +1719,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1776,6 +1788,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1851,6 +1866,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1872,6 +1890,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1917,6 +1938,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1929,6 +1953,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1938,9 +1965,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1965,6 +1989,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2025,10 +2052,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -2849,10 +2876,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2893,10 +2920,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2923,7 +2950,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -2940,7 +2967,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -2957,7 +2984,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -2974,7 +3001,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -2991,7 +3018,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -3008,7 +3035,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -3025,7 +3052,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -3042,7 +3069,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -3059,7 +3086,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -3076,7 +3103,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -3090,7 +3117,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -3104,7 +3131,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -3118,7 +3145,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -3132,7 +3159,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -3146,7 +3173,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -3160,7 +3187,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -3174,7 +3201,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -3188,7 +3215,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -3198,8 +3225,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -3210,7 +3240,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -3221,7 +3251,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3232,7 +3262,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3243,7 +3273,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3254,7 +3284,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3265,7 +3295,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3276,7 +3306,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3287,7 +3317,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3298,7 +3328,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3309,7 +3339,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3320,7 +3350,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3331,7 +3361,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3342,7 +3372,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3350,7 +3380,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3358,7 +3388,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3366,7 +3396,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3374,7 +3404,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3382,7 +3412,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3390,7 +3420,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3398,7 +3428,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3406,7 +3436,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3414,7 +3444,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3422,236 +3452,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3673,27 +3708,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3713,122 +3748,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3838,13 +3873,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BV2"/>
+  <dimension ref="A1:BW2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:74">
+    <row r="1" spans="1:75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3852,485 +3887,491 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>315</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>353</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>681</v>
+        <v>394</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="2" spans="1:74" ht="150" customHeight="1">
+        <v>765</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="2" spans="1:75" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>316</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AE2" s="2" t="s">
         <v>354</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>682</v>
+        <v>395</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>759</v>
+        <v>766</v>
+      </c>
+      <c r="BW2" s="2" t="s">
+        <v>768</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="13">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F101">
       <formula1>observedbioticrelationship</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3:X101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:Y101">
       <formula1>reassemblypostbinning</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB3:AB101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC3:AC101">
       <formula1>sourceofUViGs</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC3:AC101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD3:AD101">
       <formula1>predictedgenometype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD3:AD101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE3:AE101">
       <formula1>predictedgenomestructure</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE3:AE101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF3:AF101">
       <formula1>detectiontype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ3:AJ101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK3:AK101">
       <formula1>UViGassemblyquality</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW3:AW101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX3:AX101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ3:AZ101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA3:BA101">
       <formula1>hostpredictionapproach</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BG3:BG101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH3:BH101">
       <formula1>singlecellorviralparticlelysisapproach</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BQ3:BQ101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BR3:BR101">
       <formula1>WGAamplificationapproach</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BS3:BS101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BT3:BT101">
       <formula1>sortingtechnology</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BT3:BT101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BU3:BU101">
       <formula1>virusenrichmentapproach</formula1>
     </dataValidation>
   </dataValidations>
@@ -4340,1650 +4381,1675 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="E1:BT289"/>
+  <dimension ref="F1:BU294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="5:72">
-      <c r="E1" t="s">
-        <v>270</v>
-      </c>
-      <c r="X1" t="s">
-        <v>313</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>323</v>
+    <row r="1" spans="6:73">
+      <c r="F1" t="s">
+        <v>274</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>317</v>
       </c>
       <c r="AC1" t="s">
+        <v>327</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>338</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>350</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>355</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>367</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>396</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>696</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>716</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>739</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>745</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="2" spans="6:73">
+      <c r="F2" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>328</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>339</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>351</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>356</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>368</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>397</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>697</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>698</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>740</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>746</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="3" spans="6:73">
+      <c r="F3" t="s">
+        <v>276</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>329</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>340</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>352</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>369</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>398</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>698</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>717</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>747</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="4" spans="6:73">
+      <c r="F4" t="s">
+        <v>277</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>330</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>341</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>399</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>699</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>718</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>748</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="5" spans="6:73">
+      <c r="F5" t="s">
+        <v>278</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>116</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>342</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>400</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>700</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>749</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="6" spans="6:73">
+      <c r="AC6" t="s">
+        <v>331</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>343</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>401</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>116</v>
+      </c>
+      <c r="BT6" t="s">
+        <v>116</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="7" spans="6:73">
+      <c r="AC7" t="s">
+        <v>332</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>344</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>402</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>701</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="8" spans="6:73">
+      <c r="AC8" t="s">
+        <v>333</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>345</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>403</v>
+      </c>
+      <c r="BU8" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="9" spans="6:73">
+      <c r="AC9" t="s">
         <v>334</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD9" t="s">
         <v>346</v>
       </c>
-      <c r="AE1" t="s">
-        <v>351</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>363</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>392</v>
-      </c>
-      <c r="AZ1" t="s">
+      <c r="AX9" t="s">
+        <v>404</v>
+      </c>
+      <c r="BU9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="6:73">
+      <c r="AC10" t="s">
+        <v>335</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>347</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>405</v>
+      </c>
+      <c r="BU10" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="11" spans="6:73">
+      <c r="AX11" t="s">
+        <v>406</v>
+      </c>
+      <c r="BU11" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="12" spans="6:73">
+      <c r="AX12" t="s">
+        <v>407</v>
+      </c>
+      <c r="BU12" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="13" spans="6:73">
+      <c r="AX13" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="14" spans="6:73">
+      <c r="AX14" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="15" spans="6:73">
+      <c r="AX15" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="16" spans="6:73">
+      <c r="AX16" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="17" spans="50:50">
+      <c r="AX17" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="18" spans="50:50">
+      <c r="AX18" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="19" spans="50:50">
+      <c r="AX19" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="20" spans="50:50">
+      <c r="AX20" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="21" spans="50:50">
+      <c r="AX21" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="22" spans="50:50">
+      <c r="AX22" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="23" spans="50:50">
+      <c r="AX23" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="24" spans="50:50">
+      <c r="AX24" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="25" spans="50:50">
+      <c r="AX25" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="26" spans="50:50">
+      <c r="AX26" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="27" spans="50:50">
+      <c r="AX27" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="28" spans="50:50">
+      <c r="AX28" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="29" spans="50:50">
+      <c r="AX29" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="30" spans="50:50">
+      <c r="AX30" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="31" spans="50:50">
+      <c r="AX31" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="32" spans="50:50">
+      <c r="AX32" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="33" spans="50:50">
+      <c r="AX33" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="34" spans="50:50">
+      <c r="AX34" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="35" spans="50:50">
+      <c r="AX35" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="36" spans="50:50">
+      <c r="AX36" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="37" spans="50:50">
+      <c r="AX37" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="38" spans="50:50">
+      <c r="AX38" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="39" spans="50:50">
+      <c r="AX39" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="40" spans="50:50">
+      <c r="AX40" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="41" spans="50:50">
+      <c r="AX41" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="42" spans="50:50">
+      <c r="AX42" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="43" spans="50:50">
+      <c r="AX43" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="44" spans="50:50">
+      <c r="AX44" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="45" spans="50:50">
+      <c r="AX45" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="46" spans="50:50">
+      <c r="AX46" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="47" spans="50:50">
+      <c r="AX47" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="48" spans="50:50">
+      <c r="AX48" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="49" spans="50:50">
+      <c r="AX49" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="50" spans="50:50">
+      <c r="AX50" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="51" spans="50:50">
+      <c r="AX51" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="52" spans="50:50">
+      <c r="AX52" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="53" spans="50:50">
+      <c r="AX53" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="54" spans="50:50">
+      <c r="AX54" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="55" spans="50:50">
+      <c r="AX55" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="56" spans="50:50">
+      <c r="AX56" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="57" spans="50:50">
+      <c r="AX57" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="58" spans="50:50">
+      <c r="AX58" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="59" spans="50:50">
+      <c r="AX59" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="60" spans="50:50">
+      <c r="AX60" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="61" spans="50:50">
+      <c r="AX61" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="62" spans="50:50">
+      <c r="AX62" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="63" spans="50:50">
+      <c r="AX63" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="64" spans="50:50">
+      <c r="AX64" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="65" spans="50:50">
+      <c r="AX65" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="66" spans="50:50">
+      <c r="AX66" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="67" spans="50:50">
+      <c r="AX67" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="68" spans="50:50">
+      <c r="AX68" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="69" spans="50:50">
+      <c r="AX69" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="70" spans="50:50">
+      <c r="AX70" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="71" spans="50:50">
+      <c r="AX71" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="72" spans="50:50">
+      <c r="AX72" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="73" spans="50:50">
+      <c r="AX73" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="74" spans="50:50">
+      <c r="AX74" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="75" spans="50:50">
+      <c r="AX75" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="76" spans="50:50">
+      <c r="AX76" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="77" spans="50:50">
+      <c r="AX77" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="78" spans="50:50">
+      <c r="AX78" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="79" spans="50:50">
+      <c r="AX79" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="80" spans="50:50">
+      <c r="AX80" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="81" spans="50:50">
+      <c r="AX81" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="82" spans="50:50">
+      <c r="AX82" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="83" spans="50:50">
+      <c r="AX83" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="84" spans="50:50">
+      <c r="AX84" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="85" spans="50:50">
+      <c r="AX85" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="86" spans="50:50">
+      <c r="AX86" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="87" spans="50:50">
+      <c r="AX87" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="88" spans="50:50">
+      <c r="AX88" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="89" spans="50:50">
+      <c r="AX89" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="90" spans="50:50">
+      <c r="AX90" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="91" spans="50:50">
+      <c r="AX91" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="92" spans="50:50">
+      <c r="AX92" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="93" spans="50:50">
+      <c r="AX93" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="94" spans="50:50">
+      <c r="AX94" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="95" spans="50:50">
+      <c r="AX95" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="96" spans="50:50">
+      <c r="AX96" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="97" spans="50:50">
+      <c r="AX97" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="98" spans="50:50">
+      <c r="AX98" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="99" spans="50:50">
+      <c r="AX99" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="100" spans="50:50">
+      <c r="AX100" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="101" spans="50:50">
+      <c r="AX101" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="102" spans="50:50">
+      <c r="AX102" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="103" spans="50:50">
+      <c r="AX103" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="104" spans="50:50">
+      <c r="AX104" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="105" spans="50:50">
+      <c r="AX105" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="106" spans="50:50">
+      <c r="AX106" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="107" spans="50:50">
+      <c r="AX107" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="108" spans="50:50">
+      <c r="AX108" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="109" spans="50:50">
+      <c r="AX109" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="110" spans="50:50">
+      <c r="AX110" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="111" spans="50:50">
+      <c r="AX111" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="112" spans="50:50">
+      <c r="AX112" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="113" spans="50:50">
+      <c r="AX113" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="114" spans="50:50">
+      <c r="AX114" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="115" spans="50:50">
+      <c r="AX115" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="116" spans="50:50">
+      <c r="AX116" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="117" spans="50:50">
+      <c r="AX117" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="118" spans="50:50">
+      <c r="AX118" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="119" spans="50:50">
+      <c r="AX119" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="120" spans="50:50">
+      <c r="AX120" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="121" spans="50:50">
+      <c r="AX121" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="122" spans="50:50">
+      <c r="AX122" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="123" spans="50:50">
+      <c r="AX123" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="124" spans="50:50">
+      <c r="AX124" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="125" spans="50:50">
+      <c r="AX125" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="126" spans="50:50">
+      <c r="AX126" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="127" spans="50:50">
+      <c r="AX127" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="128" spans="50:50">
+      <c r="AX128" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="129" spans="50:50">
+      <c r="AX129" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="130" spans="50:50">
+      <c r="AX130" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="131" spans="50:50">
+      <c r="AX131" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="132" spans="50:50">
+      <c r="AX132" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="133" spans="50:50">
+      <c r="AX133" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="134" spans="50:50">
+      <c r="AX134" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="135" spans="50:50">
+      <c r="AX135" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="136" spans="50:50">
+      <c r="AX136" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="137" spans="50:50">
+      <c r="AX137" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="138" spans="50:50">
+      <c r="AX138" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="139" spans="50:50">
+      <c r="AX139" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="140" spans="50:50">
+      <c r="AX140" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="141" spans="50:50">
+      <c r="AX141" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="142" spans="50:50">
+      <c r="AX142" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="143" spans="50:50">
+      <c r="AX143" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="144" spans="50:50">
+      <c r="AX144" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="145" spans="50:50">
+      <c r="AX145" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="146" spans="50:50">
+      <c r="AX146" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="147" spans="50:50">
+      <c r="AX147" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="148" spans="50:50">
+      <c r="AX148" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="149" spans="50:50">
+      <c r="AX149" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="150" spans="50:50">
+      <c r="AX150" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="151" spans="50:50">
+      <c r="AX151" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="152" spans="50:50">
+      <c r="AX152" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="153" spans="50:50">
+      <c r="AX153" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="154" spans="50:50">
+      <c r="AX154" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="155" spans="50:50">
+      <c r="AX155" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="156" spans="50:50">
+      <c r="AX156" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="157" spans="50:50">
+      <c r="AX157" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="158" spans="50:50">
+      <c r="AX158" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="159" spans="50:50">
+      <c r="AX159" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="160" spans="50:50">
+      <c r="AX160" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="161" spans="50:50">
+      <c r="AX161" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="162" spans="50:50">
+      <c r="AX162" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="163" spans="50:50">
+      <c r="AX163" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="164" spans="50:50">
+      <c r="AX164" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="165" spans="50:50">
+      <c r="AX165" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="166" spans="50:50">
+      <c r="AX166" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="167" spans="50:50">
+      <c r="AX167" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="168" spans="50:50">
+      <c r="AX168" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="169" spans="50:50">
+      <c r="AX169" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="170" spans="50:50">
+      <c r="AX170" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="171" spans="50:50">
+      <c r="AX171" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="172" spans="50:50">
+      <c r="AX172" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="173" spans="50:50">
+      <c r="AX173" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="174" spans="50:50">
+      <c r="AX174" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="175" spans="50:50">
+      <c r="AX175" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="176" spans="50:50">
+      <c r="AX176" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="177" spans="50:50">
+      <c r="AX177" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="178" spans="50:50">
+      <c r="AX178" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="179" spans="50:50">
+      <c r="AX179" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="180" spans="50:50">
+      <c r="AX180" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="181" spans="50:50">
+      <c r="AX181" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="182" spans="50:50">
+      <c r="AX182" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="183" spans="50:50">
+      <c r="AX183" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="184" spans="50:50">
+      <c r="AX184" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="185" spans="50:50">
+      <c r="AX185" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="186" spans="50:50">
+      <c r="AX186" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="187" spans="50:50">
+      <c r="AX187" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="188" spans="50:50">
+      <c r="AX188" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="189" spans="50:50">
+      <c r="AX189" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="190" spans="50:50">
+      <c r="AX190" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="191" spans="50:50">
+      <c r="AX191" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="192" spans="50:50">
+      <c r="AX192" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="193" spans="50:50">
+      <c r="AX193" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="194" spans="50:50">
+      <c r="AX194" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="195" spans="50:50">
+      <c r="AX195" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="196" spans="50:50">
+      <c r="AX196" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="197" spans="50:50">
+      <c r="AX197" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="198" spans="50:50">
+      <c r="AX198" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="199" spans="50:50">
+      <c r="AX199" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="200" spans="50:50">
+      <c r="AX200" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="201" spans="50:50">
+      <c r="AX201" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="202" spans="50:50">
+      <c r="AX202" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="203" spans="50:50">
+      <c r="AX203" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="204" spans="50:50">
+      <c r="AX204" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="205" spans="50:50">
+      <c r="AX205" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="206" spans="50:50">
+      <c r="AX206" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="207" spans="50:50">
+      <c r="AX207" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="208" spans="50:50">
+      <c r="AX208" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="209" spans="50:50">
+      <c r="AX209" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="210" spans="50:50">
+      <c r="AX210" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="211" spans="50:50">
+      <c r="AX211" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="212" spans="50:50">
+      <c r="AX212" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="213" spans="50:50">
+      <c r="AX213" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="214" spans="50:50">
+      <c r="AX214" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="215" spans="50:50">
+      <c r="AX215" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="216" spans="50:50">
+      <c r="AX216" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="217" spans="50:50">
+      <c r="AX217" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="218" spans="50:50">
+      <c r="AX218" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="219" spans="50:50">
+      <c r="AX219" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="220" spans="50:50">
+      <c r="AX220" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="221" spans="50:50">
+      <c r="AX221" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="222" spans="50:50">
+      <c r="AX222" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="223" spans="50:50">
+      <c r="AX223" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="224" spans="50:50">
+      <c r="AX224" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="225" spans="50:50">
+      <c r="AX225" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="226" spans="50:50">
+      <c r="AX226" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="227" spans="50:50">
+      <c r="AX227" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="228" spans="50:50">
+      <c r="AX228" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="229" spans="50:50">
+      <c r="AX229" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="230" spans="50:50">
+      <c r="AX230" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="231" spans="50:50">
+      <c r="AX231" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="232" spans="50:50">
+      <c r="AX232" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="233" spans="50:50">
+      <c r="AX233" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="234" spans="50:50">
+      <c r="AX234" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="235" spans="50:50">
+      <c r="AX235" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="236" spans="50:50">
+      <c r="AX236" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="237" spans="50:50">
+      <c r="AX237" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="238" spans="50:50">
+      <c r="AX238" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="239" spans="50:50">
+      <c r="AX239" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="240" spans="50:50">
+      <c r="AX240" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="241" spans="50:50">
+      <c r="AX241" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="242" spans="50:50">
+      <c r="AX242" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="243" spans="50:50">
+      <c r="AX243" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="244" spans="50:50">
+      <c r="AX244" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="245" spans="50:50">
+      <c r="AX245" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="246" spans="50:50">
+      <c r="AX246" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="247" spans="50:50">
+      <c r="AX247" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="248" spans="50:50">
+      <c r="AX248" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="249" spans="50:50">
+      <c r="AX249" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="250" spans="50:50">
+      <c r="AX250" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="251" spans="50:50">
+      <c r="AX251" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="252" spans="50:50">
+      <c r="AX252" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="253" spans="50:50">
+      <c r="AX253" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="254" spans="50:50">
+      <c r="AX254" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="255" spans="50:50">
+      <c r="AX255" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="256" spans="50:50">
+      <c r="AX256" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="257" spans="50:50">
+      <c r="AX257" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="258" spans="50:50">
+      <c r="AX258" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="259" spans="50:50">
+      <c r="AX259" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="260" spans="50:50">
+      <c r="AX260" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="261" spans="50:50">
+      <c r="AX261" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="262" spans="50:50">
+      <c r="AX262" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="263" spans="50:50">
+      <c r="AX263" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="264" spans="50:50">
+      <c r="AX264" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="265" spans="50:50">
+      <c r="AX265" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="266" spans="50:50">
+      <c r="AX266" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="267" spans="50:50">
+      <c r="AX267" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="268" spans="50:50">
+      <c r="AX268" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="269" spans="50:50">
+      <c r="AX269" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="270" spans="50:50">
+      <c r="AX270" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="271" spans="50:50">
+      <c r="AX271" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="272" spans="50:50">
+      <c r="AX272" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="273" spans="50:50">
+      <c r="AX273" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="274" spans="50:50">
+      <c r="AX274" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="275" spans="50:50">
+      <c r="AX275" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="276" spans="50:50">
+      <c r="AX276" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="277" spans="50:50">
+      <c r="AX277" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="278" spans="50:50">
+      <c r="AX278" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="279" spans="50:50">
+      <c r="AX279" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="280" spans="50:50">
+      <c r="AX280" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="281" spans="50:50">
+      <c r="AX281" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="282" spans="50:50">
+      <c r="AX282" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="283" spans="50:50">
+      <c r="AX283" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="284" spans="50:50">
+      <c r="AX284" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="285" spans="50:50">
+      <c r="AX285" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="286" spans="50:50">
+      <c r="AX286" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="287" spans="50:50">
+      <c r="AX287" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="288" spans="50:50">
+      <c r="AX288" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="289" spans="50:50">
+      <c r="AX289" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="290" spans="50:50">
+      <c r="AX290" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="291" spans="50:50">
+      <c r="AX291" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="292" spans="50:50">
+      <c r="AX292" t="s">
         <v>687</v>
       </c>
-      <c r="BG1" t="s">
-        <v>707</v>
-      </c>
-      <c r="BQ1" t="s">
-        <v>730</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>736</v>
-      </c>
-      <c r="BT1" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="2" spans="5:72">
-      <c r="E2" t="s">
-        <v>271</v>
-      </c>
-      <c r="X2" t="s">
-        <v>314</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>324</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>335</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>347</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>352</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>364</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>393</v>
-      </c>
-      <c r="AZ2" t="s">
+    </row>
+    <row r="293" spans="50:50">
+      <c r="AX293" t="s">
         <v>688</v>
       </c>
-      <c r="BG2" t="s">
+    </row>
+    <row r="294" spans="50:50">
+      <c r="AX294" t="s">
         <v>689</v>
-      </c>
-      <c r="BQ2" t="s">
-        <v>731</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>737</v>
-      </c>
-      <c r="BT2" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="3" spans="5:72">
-      <c r="E3" t="s">
-        <v>272</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>325</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>336</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>348</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>365</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>394</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>689</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>708</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>738</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="4" spans="5:72">
-      <c r="E4" t="s">
-        <v>273</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>326</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>337</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>395</v>
-      </c>
-      <c r="AZ4" t="s">
-        <v>690</v>
-      </c>
-      <c r="BG4" t="s">
-        <v>709</v>
-      </c>
-      <c r="BS4" t="s">
-        <v>739</v>
-      </c>
-      <c r="BT4" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="5" spans="5:72">
-      <c r="E5" t="s">
-        <v>274</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>116</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>338</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>396</v>
-      </c>
-      <c r="AZ5" t="s">
-        <v>691</v>
-      </c>
-      <c r="BS5" t="s">
-        <v>740</v>
-      </c>
-      <c r="BT5" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="6" spans="5:72">
-      <c r="AB6" t="s">
-        <v>327</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>339</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>397</v>
-      </c>
-      <c r="AZ6" t="s">
-        <v>116</v>
-      </c>
-      <c r="BS6" t="s">
-        <v>116</v>
-      </c>
-      <c r="BT6" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="7" spans="5:72">
-      <c r="AB7" t="s">
-        <v>328</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>340</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>398</v>
-      </c>
-      <c r="AZ7" t="s">
-        <v>692</v>
-      </c>
-      <c r="BT7" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="8" spans="5:72">
-      <c r="AB8" t="s">
-        <v>329</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>341</v>
-      </c>
-      <c r="AW8" t="s">
-        <v>399</v>
-      </c>
-      <c r="BT8" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="9" spans="5:72">
-      <c r="AB9" t="s">
-        <v>330</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>342</v>
-      </c>
-      <c r="AW9" t="s">
-        <v>400</v>
-      </c>
-      <c r="BT9" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="10" spans="5:72">
-      <c r="AB10" t="s">
-        <v>331</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>343</v>
-      </c>
-      <c r="AW10" t="s">
-        <v>401</v>
-      </c>
-      <c r="BT10" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="11" spans="5:72">
-      <c r="AW11" t="s">
-        <v>402</v>
-      </c>
-      <c r="BT11" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="12" spans="5:72">
-      <c r="AW12" t="s">
-        <v>403</v>
-      </c>
-      <c r="BT12" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="13" spans="5:72">
-      <c r="AW13" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="14" spans="5:72">
-      <c r="AW14" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="15" spans="5:72">
-      <c r="AW15" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="16" spans="5:72">
-      <c r="AW16" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="17" spans="49:49">
-      <c r="AW17" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="18" spans="49:49">
-      <c r="AW18" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="19" spans="49:49">
-      <c r="AW19" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="20" spans="49:49">
-      <c r="AW20" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="21" spans="49:49">
-      <c r="AW21" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="22" spans="49:49">
-      <c r="AW22" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="23" spans="49:49">
-      <c r="AW23" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="24" spans="49:49">
-      <c r="AW24" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="25" spans="49:49">
-      <c r="AW25" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="26" spans="49:49">
-      <c r="AW26" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="27" spans="49:49">
-      <c r="AW27" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="28" spans="49:49">
-      <c r="AW28" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="29" spans="49:49">
-      <c r="AW29" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="30" spans="49:49">
-      <c r="AW30" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="31" spans="49:49">
-      <c r="AW31" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="32" spans="49:49">
-      <c r="AW32" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="33" spans="49:49">
-      <c r="AW33" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="34" spans="49:49">
-      <c r="AW34" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="35" spans="49:49">
-      <c r="AW35" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="36" spans="49:49">
-      <c r="AW36" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="37" spans="49:49">
-      <c r="AW37" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="38" spans="49:49">
-      <c r="AW38" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="39" spans="49:49">
-      <c r="AW39" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="40" spans="49:49">
-      <c r="AW40" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="41" spans="49:49">
-      <c r="AW41" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="42" spans="49:49">
-      <c r="AW42" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="43" spans="49:49">
-      <c r="AW43" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="44" spans="49:49">
-      <c r="AW44" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="45" spans="49:49">
-      <c r="AW45" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="46" spans="49:49">
-      <c r="AW46" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="47" spans="49:49">
-      <c r="AW47" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="48" spans="49:49">
-      <c r="AW48" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="49" spans="49:49">
-      <c r="AW49" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="50" spans="49:49">
-      <c r="AW50" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="51" spans="49:49">
-      <c r="AW51" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="52" spans="49:49">
-      <c r="AW52" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="53" spans="49:49">
-      <c r="AW53" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="54" spans="49:49">
-      <c r="AW54" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="55" spans="49:49">
-      <c r="AW55" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="56" spans="49:49">
-      <c r="AW56" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="57" spans="49:49">
-      <c r="AW57" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="58" spans="49:49">
-      <c r="AW58" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="59" spans="49:49">
-      <c r="AW59" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="60" spans="49:49">
-      <c r="AW60" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="61" spans="49:49">
-      <c r="AW61" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="62" spans="49:49">
-      <c r="AW62" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="63" spans="49:49">
-      <c r="AW63" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="64" spans="49:49">
-      <c r="AW64" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="65" spans="49:49">
-      <c r="AW65" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="66" spans="49:49">
-      <c r="AW66" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="67" spans="49:49">
-      <c r="AW67" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="68" spans="49:49">
-      <c r="AW68" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="69" spans="49:49">
-      <c r="AW69" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="70" spans="49:49">
-      <c r="AW70" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="71" spans="49:49">
-      <c r="AW71" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="72" spans="49:49">
-      <c r="AW72" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="73" spans="49:49">
-      <c r="AW73" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="74" spans="49:49">
-      <c r="AW74" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="75" spans="49:49">
-      <c r="AW75" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="76" spans="49:49">
-      <c r="AW76" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="77" spans="49:49">
-      <c r="AW77" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="78" spans="49:49">
-      <c r="AW78" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="79" spans="49:49">
-      <c r="AW79" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="80" spans="49:49">
-      <c r="AW80" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="81" spans="49:49">
-      <c r="AW81" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="82" spans="49:49">
-      <c r="AW82" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="83" spans="49:49">
-      <c r="AW83" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="84" spans="49:49">
-      <c r="AW84" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="85" spans="49:49">
-      <c r="AW85" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="86" spans="49:49">
-      <c r="AW86" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="87" spans="49:49">
-      <c r="AW87" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="88" spans="49:49">
-      <c r="AW88" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="89" spans="49:49">
-      <c r="AW89" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="90" spans="49:49">
-      <c r="AW90" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="91" spans="49:49">
-      <c r="AW91" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="92" spans="49:49">
-      <c r="AW92" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="93" spans="49:49">
-      <c r="AW93" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="94" spans="49:49">
-      <c r="AW94" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="95" spans="49:49">
-      <c r="AW95" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="96" spans="49:49">
-      <c r="AW96" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="97" spans="49:49">
-      <c r="AW97" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="98" spans="49:49">
-      <c r="AW98" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="99" spans="49:49">
-      <c r="AW99" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="100" spans="49:49">
-      <c r="AW100" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="101" spans="49:49">
-      <c r="AW101" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="102" spans="49:49">
-      <c r="AW102" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="103" spans="49:49">
-      <c r="AW103" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="104" spans="49:49">
-      <c r="AW104" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="105" spans="49:49">
-      <c r="AW105" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="106" spans="49:49">
-      <c r="AW106" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="107" spans="49:49">
-      <c r="AW107" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="108" spans="49:49">
-      <c r="AW108" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="109" spans="49:49">
-      <c r="AW109" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="110" spans="49:49">
-      <c r="AW110" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="111" spans="49:49">
-      <c r="AW111" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="112" spans="49:49">
-      <c r="AW112" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="113" spans="49:49">
-      <c r="AW113" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="114" spans="49:49">
-      <c r="AW114" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="115" spans="49:49">
-      <c r="AW115" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="116" spans="49:49">
-      <c r="AW116" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="117" spans="49:49">
-      <c r="AW117" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="118" spans="49:49">
-      <c r="AW118" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="119" spans="49:49">
-      <c r="AW119" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="120" spans="49:49">
-      <c r="AW120" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="121" spans="49:49">
-      <c r="AW121" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="122" spans="49:49">
-      <c r="AW122" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="123" spans="49:49">
-      <c r="AW123" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="124" spans="49:49">
-      <c r="AW124" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="125" spans="49:49">
-      <c r="AW125" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="126" spans="49:49">
-      <c r="AW126" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="127" spans="49:49">
-      <c r="AW127" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="128" spans="49:49">
-      <c r="AW128" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="129" spans="49:49">
-      <c r="AW129" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="130" spans="49:49">
-      <c r="AW130" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="131" spans="49:49">
-      <c r="AW131" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="132" spans="49:49">
-      <c r="AW132" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="133" spans="49:49">
-      <c r="AW133" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="134" spans="49:49">
-      <c r="AW134" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="135" spans="49:49">
-      <c r="AW135" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="136" spans="49:49">
-      <c r="AW136" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="137" spans="49:49">
-      <c r="AW137" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="138" spans="49:49">
-      <c r="AW138" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="139" spans="49:49">
-      <c r="AW139" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="140" spans="49:49">
-      <c r="AW140" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="141" spans="49:49">
-      <c r="AW141" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="142" spans="49:49">
-      <c r="AW142" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="143" spans="49:49">
-      <c r="AW143" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="144" spans="49:49">
-      <c r="AW144" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="145" spans="49:49">
-      <c r="AW145" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="146" spans="49:49">
-      <c r="AW146" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="147" spans="49:49">
-      <c r="AW147" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="148" spans="49:49">
-      <c r="AW148" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="149" spans="49:49">
-      <c r="AW149" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="150" spans="49:49">
-      <c r="AW150" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="151" spans="49:49">
-      <c r="AW151" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="152" spans="49:49">
-      <c r="AW152" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="153" spans="49:49">
-      <c r="AW153" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="154" spans="49:49">
-      <c r="AW154" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="155" spans="49:49">
-      <c r="AW155" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="156" spans="49:49">
-      <c r="AW156" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="157" spans="49:49">
-      <c r="AW157" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="158" spans="49:49">
-      <c r="AW158" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="159" spans="49:49">
-      <c r="AW159" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="160" spans="49:49">
-      <c r="AW160" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="161" spans="49:49">
-      <c r="AW161" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="162" spans="49:49">
-      <c r="AW162" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="163" spans="49:49">
-      <c r="AW163" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="164" spans="49:49">
-      <c r="AW164" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="165" spans="49:49">
-      <c r="AW165" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="166" spans="49:49">
-      <c r="AW166" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="167" spans="49:49">
-      <c r="AW167" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="168" spans="49:49">
-      <c r="AW168" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="169" spans="49:49">
-      <c r="AW169" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="170" spans="49:49">
-      <c r="AW170" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="171" spans="49:49">
-      <c r="AW171" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="172" spans="49:49">
-      <c r="AW172" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="173" spans="49:49">
-      <c r="AW173" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="174" spans="49:49">
-      <c r="AW174" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="175" spans="49:49">
-      <c r="AW175" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="176" spans="49:49">
-      <c r="AW176" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="177" spans="49:49">
-      <c r="AW177" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="178" spans="49:49">
-      <c r="AW178" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="179" spans="49:49">
-      <c r="AW179" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="180" spans="49:49">
-      <c r="AW180" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="181" spans="49:49">
-      <c r="AW181" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="182" spans="49:49">
-      <c r="AW182" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="183" spans="49:49">
-      <c r="AW183" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="184" spans="49:49">
-      <c r="AW184" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="185" spans="49:49">
-      <c r="AW185" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="186" spans="49:49">
-      <c r="AW186" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="187" spans="49:49">
-      <c r="AW187" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="188" spans="49:49">
-      <c r="AW188" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="189" spans="49:49">
-      <c r="AW189" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="190" spans="49:49">
-      <c r="AW190" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="191" spans="49:49">
-      <c r="AW191" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="192" spans="49:49">
-      <c r="AW192" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="193" spans="49:49">
-      <c r="AW193" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="194" spans="49:49">
-      <c r="AW194" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="195" spans="49:49">
-      <c r="AW195" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="196" spans="49:49">
-      <c r="AW196" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="197" spans="49:49">
-      <c r="AW197" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="198" spans="49:49">
-      <c r="AW198" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="199" spans="49:49">
-      <c r="AW199" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="200" spans="49:49">
-      <c r="AW200" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="201" spans="49:49">
-      <c r="AW201" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="202" spans="49:49">
-      <c r="AW202" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="203" spans="49:49">
-      <c r="AW203" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="204" spans="49:49">
-      <c r="AW204" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="205" spans="49:49">
-      <c r="AW205" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="206" spans="49:49">
-      <c r="AW206" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="207" spans="49:49">
-      <c r="AW207" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="208" spans="49:49">
-      <c r="AW208" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="209" spans="49:49">
-      <c r="AW209" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="210" spans="49:49">
-      <c r="AW210" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="211" spans="49:49">
-      <c r="AW211" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="212" spans="49:49">
-      <c r="AW212" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="213" spans="49:49">
-      <c r="AW213" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="214" spans="49:49">
-      <c r="AW214" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="215" spans="49:49">
-      <c r="AW215" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="216" spans="49:49">
-      <c r="AW216" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="217" spans="49:49">
-      <c r="AW217" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="218" spans="49:49">
-      <c r="AW218" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="219" spans="49:49">
-      <c r="AW219" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="220" spans="49:49">
-      <c r="AW220" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="221" spans="49:49">
-      <c r="AW221" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="222" spans="49:49">
-      <c r="AW222" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="223" spans="49:49">
-      <c r="AW223" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="224" spans="49:49">
-      <c r="AW224" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="225" spans="49:49">
-      <c r="AW225" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="226" spans="49:49">
-      <c r="AW226" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="227" spans="49:49">
-      <c r="AW227" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="228" spans="49:49">
-      <c r="AW228" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="229" spans="49:49">
-      <c r="AW229" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="230" spans="49:49">
-      <c r="AW230" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="231" spans="49:49">
-      <c r="AW231" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="232" spans="49:49">
-      <c r="AW232" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="233" spans="49:49">
-      <c r="AW233" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="234" spans="49:49">
-      <c r="AW234" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="235" spans="49:49">
-      <c r="AW235" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="236" spans="49:49">
-      <c r="AW236" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="237" spans="49:49">
-      <c r="AW237" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="238" spans="49:49">
-      <c r="AW238" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="239" spans="49:49">
-      <c r="AW239" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="240" spans="49:49">
-      <c r="AW240" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="241" spans="49:49">
-      <c r="AW241" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="242" spans="49:49">
-      <c r="AW242" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="243" spans="49:49">
-      <c r="AW243" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="244" spans="49:49">
-      <c r="AW244" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="245" spans="49:49">
-      <c r="AW245" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="246" spans="49:49">
-      <c r="AW246" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="247" spans="49:49">
-      <c r="AW247" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="248" spans="49:49">
-      <c r="AW248" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="249" spans="49:49">
-      <c r="AW249" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="250" spans="49:49">
-      <c r="AW250" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="251" spans="49:49">
-      <c r="AW251" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="252" spans="49:49">
-      <c r="AW252" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="253" spans="49:49">
-      <c r="AW253" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="254" spans="49:49">
-      <c r="AW254" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="255" spans="49:49">
-      <c r="AW255" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="256" spans="49:49">
-      <c r="AW256" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="257" spans="49:49">
-      <c r="AW257" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="258" spans="49:49">
-      <c r="AW258" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="259" spans="49:49">
-      <c r="AW259" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="260" spans="49:49">
-      <c r="AW260" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="261" spans="49:49">
-      <c r="AW261" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="262" spans="49:49">
-      <c r="AW262" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="263" spans="49:49">
-      <c r="AW263" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="264" spans="49:49">
-      <c r="AW264" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="265" spans="49:49">
-      <c r="AW265" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="266" spans="49:49">
-      <c r="AW266" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="267" spans="49:49">
-      <c r="AW267" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="268" spans="49:49">
-      <c r="AW268" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="269" spans="49:49">
-      <c r="AW269" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="270" spans="49:49">
-      <c r="AW270" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="271" spans="49:49">
-      <c r="AW271" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="272" spans="49:49">
-      <c r="AW272" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="273" spans="49:49">
-      <c r="AW273" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="274" spans="49:49">
-      <c r="AW274" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="275" spans="49:49">
-      <c r="AW275" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="276" spans="49:49">
-      <c r="AW276" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="277" spans="49:49">
-      <c r="AW277" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="278" spans="49:49">
-      <c r="AW278" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="279" spans="49:49">
-      <c r="AW279" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="280" spans="49:49">
-      <c r="AW280" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="281" spans="49:49">
-      <c r="AW281" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="282" spans="49:49">
-      <c r="AW282" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="283" spans="49:49">
-      <c r="AW283" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="284" spans="49:49">
-      <c r="AW284" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="285" spans="49:49">
-      <c r="AW285" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="286" spans="49:49">
-      <c r="AW286" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="287" spans="49:49">
-      <c r="AW287" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="288" spans="49:49">
-      <c r="AW288" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="289" spans="49:49">
-      <c r="AW289" t="s">
-        <v>680</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000049/metadata_template_ERC000049.xlsx
+++ b/templates/ERC000049/metadata_template_ERC000049.xlsx
@@ -17,33 +17,33 @@
     <sheet name="cv_sample" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="detectiontype">'cv_sample'!$AF$1:$AF$2</definedName>
+    <definedName name="detectiontype">'cv_sample'!$AG$1:$AG$2</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AX$1:$AX$294</definedName>
-    <definedName name="hostpredictionapproach">'cv_sample'!$BA$1:$BA$7</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AY$1:$AY$294</definedName>
+    <definedName name="hostpredictionapproach">'cv_sample'!$BB$1:$BB$7</definedName>
     <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="observedbioticrelationship">'cv_sample'!$F$1:$F$5</definedName>
+    <definedName name="observedbioticrelationship">'cv_sample'!$G$1:$G$5</definedName>
     <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
-    <definedName name="predictedgenomestructure">'cv_sample'!$AE$1:$AE$3</definedName>
-    <definedName name="predictedgenometype">'cv_sample'!$AD$1:$AD$10</definedName>
-    <definedName name="reassemblypostbinning">'cv_sample'!$Y$1:$Y$2</definedName>
-    <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$BH$1:$BH$4</definedName>
-    <definedName name="sortingtechnology">'cv_sample'!$BT$1:$BT$6</definedName>
-    <definedName name="sourceofUViGs">'cv_sample'!$AC$1:$AC$10</definedName>
+    <definedName name="predictedgenomestructure">'cv_sample'!$AF$1:$AF$3</definedName>
+    <definedName name="predictedgenometype">'cv_sample'!$AE$1:$AE$10</definedName>
+    <definedName name="reassemblypostbinning">'cv_sample'!$Z$1:$Z$2</definedName>
+    <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$BI$1:$BI$4</definedName>
+    <definedName name="sortingtechnology">'cv_sample'!$BU$1:$BU$6</definedName>
+    <definedName name="sourceofUViGs">'cv_sample'!$AD$1:$AD$10</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="UViGassemblyquality">'cv_sample'!$AK$1:$AK$3</definedName>
-    <definedName name="virusenrichmentapproach">'cv_sample'!$BU$1:$BU$12</definedName>
-    <definedName name="WGAamplificationapproach">'cv_sample'!$BR$1:$BR$2</definedName>
+    <definedName name="UViGassemblyquality">'cv_sample'!$AL$1:$AL$3</definedName>
+    <definedName name="virusenrichmentapproach">'cv_sample'!$BV$1:$BV$12</definedName>
+    <definedName name="WGAamplificationapproach">'cv_sample'!$BS$1:$BS$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="771">
   <si>
     <t>alias</t>
   </si>
@@ -859,6 +859,12 @@
   </si>
   <si>
     <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
+    <t>common_name</t>
+  </si>
+  <si>
+    <t>(Optional) Genbank common name of the organism.  examples: human, mouse.</t>
   </si>
   <si>
     <t>sample_description</t>
@@ -3873,13 +3879,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BW2"/>
+  <dimension ref="A1:BX2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:75">
+    <row r="1" spans="1:76">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3896,7 +3902,7 @@
         <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>281</v>
@@ -3953,7 +3959,7 @@
         <v>315</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>321</v>
@@ -3965,16 +3971,16 @@
         <v>325</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG1" s="1" t="s">
         <v>359</v>
@@ -3989,7 +3995,7 @@
         <v>365</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="AL1" s="1" t="s">
         <v>372</v>
@@ -4028,7 +4034,7 @@
         <v>394</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>690</v>
+        <v>396</v>
       </c>
       <c r="AY1" s="1" t="s">
         <v>692</v>
@@ -4037,7 +4043,7 @@
         <v>694</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="BB1" s="1" t="s">
         <v>704</v>
@@ -4058,7 +4064,7 @@
         <v>714</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="BI1" s="1" t="s">
         <v>721</v>
@@ -4088,16 +4094,16 @@
         <v>737</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="BS1" s="1" t="s">
         <v>743</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>763</v>
+        <v>752</v>
       </c>
       <c r="BV1" s="1" t="s">
         <v>765</v>
@@ -4105,8 +4111,11 @@
       <c r="BW1" s="1" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="2" spans="1:75" ht="150" customHeight="1">
+      <c r="BX1" s="1" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="2" spans="1:76" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>266</v>
       </c>
@@ -4123,7 +4132,7 @@
         <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>282</v>
@@ -4180,7 +4189,7 @@
         <v>316</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="Z2" s="2" t="s">
         <v>322</v>
@@ -4192,16 +4201,16 @@
         <v>326</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AG2" s="2" t="s">
         <v>360</v>
@@ -4216,7 +4225,7 @@
         <v>366</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="AL2" s="2" t="s">
         <v>373</v>
@@ -4255,7 +4264,7 @@
         <v>395</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>691</v>
+        <v>397</v>
       </c>
       <c r="AY2" s="2" t="s">
         <v>693</v>
@@ -4264,7 +4273,7 @@
         <v>695</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="BB2" s="2" t="s">
         <v>705</v>
@@ -4285,7 +4294,7 @@
         <v>715</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="BI2" s="2" t="s">
         <v>722</v>
@@ -4315,16 +4324,16 @@
         <v>738</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="BS2" s="2" t="s">
         <v>744</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>764</v>
+        <v>753</v>
       </c>
       <c r="BV2" s="2" t="s">
         <v>766</v>
@@ -4332,46 +4341,49 @@
       <c r="BW2" s="2" t="s">
         <v>768</v>
       </c>
+      <c r="BX2" s="2" t="s">
+        <v>770</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="13">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G101">
       <formula1>observedbioticrelationship</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3:Y101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z3:Z101">
       <formula1>reassemblypostbinning</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC3:AC101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD3:AD101">
       <formula1>sourceofUViGs</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD3:AD101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE3:AE101">
       <formula1>predictedgenometype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE3:AE101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF3:AF101">
       <formula1>predictedgenomestructure</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF3:AF101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG3:AG101">
       <formula1>detectiontype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK3:AK101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL3:AL101">
       <formula1>UViGassemblyquality</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX3:AX101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY3:AY101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA3:BA101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BB3:BB101">
       <formula1>hostpredictionapproach</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH3:BH101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI3:BI101">
       <formula1>singlecellorviralparticlelysisapproach</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BR3:BR101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BS3:BS101">
       <formula1>WGAamplificationapproach</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BT3:BT101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BU3:BU101">
       <formula1>sortingtechnology</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BU3:BU101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BV3:BV101">
       <formula1>virusenrichmentapproach</formula1>
     </dataValidation>
   </dataValidations>
@@ -4381,1675 +4393,1675 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="F1:BU294"/>
+  <dimension ref="G1:BV294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="6:73">
-      <c r="F1" t="s">
-        <v>274</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>317</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>327</v>
+    <row r="1" spans="7:74">
+      <c r="G1" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>319</v>
       </c>
       <c r="AD1" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="AE1" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AF1" t="s">
-        <v>355</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>367</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>396</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>696</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>716</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>739</v>
-      </c>
-      <c r="BT1" t="s">
-        <v>745</v>
+        <v>352</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>357</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>369</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>398</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>698</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>718</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>741</v>
       </c>
       <c r="BU1" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="2" spans="6:73">
-      <c r="F2" t="s">
-        <v>275</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>318</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>328</v>
+        <v>747</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="2" spans="7:74">
+      <c r="G2" t="s">
+        <v>277</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>320</v>
       </c>
       <c r="AD2" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="AE2" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="AF2" t="s">
-        <v>356</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>368</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>397</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>697</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>698</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>740</v>
-      </c>
-      <c r="BT2" t="s">
-        <v>746</v>
+        <v>353</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>358</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>370</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>399</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>699</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>700</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>742</v>
       </c>
       <c r="BU2" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="3" spans="6:73">
-      <c r="F3" t="s">
-        <v>276</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>329</v>
+        <v>748</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="3" spans="7:74">
+      <c r="G3" t="s">
+        <v>278</v>
       </c>
       <c r="AD3" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="AE3" t="s">
-        <v>352</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>369</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>398</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>698</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>717</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>747</v>
+        <v>342</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>354</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>371</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>400</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>700</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>719</v>
       </c>
       <c r="BU3" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="4" spans="6:73">
-      <c r="F4" t="s">
-        <v>277</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>330</v>
+        <v>749</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="4" spans="7:74">
+      <c r="G4" t="s">
+        <v>279</v>
       </c>
       <c r="AD4" t="s">
-        <v>341</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>399</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>699</v>
-      </c>
-      <c r="BH4" t="s">
-        <v>718</v>
-      </c>
-      <c r="BT4" t="s">
-        <v>748</v>
+        <v>332</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>343</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>401</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>701</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>720</v>
       </c>
       <c r="BU4" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="5" spans="6:73">
-      <c r="F5" t="s">
-        <v>278</v>
-      </c>
-      <c r="AC5" t="s">
+        <v>750</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="5" spans="7:74">
+      <c r="G5" t="s">
+        <v>280</v>
+      </c>
+      <c r="AD5" t="s">
         <v>116</v>
       </c>
-      <c r="AD5" t="s">
-        <v>342</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>400</v>
-      </c>
-      <c r="BA5" t="s">
-        <v>700</v>
-      </c>
-      <c r="BT5" t="s">
-        <v>749</v>
+      <c r="AE5" t="s">
+        <v>344</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>402</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>702</v>
       </c>
       <c r="BU5" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="6" spans="6:73">
-      <c r="AC6" t="s">
-        <v>331</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="6" spans="7:74">
       <c r="AD6" t="s">
-        <v>343</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>401</v>
-      </c>
-      <c r="BA6" t="s">
+        <v>333</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>345</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>403</v>
+      </c>
+      <c r="BB6" t="s">
         <v>116</v>
       </c>
-      <c r="BT6" t="s">
+      <c r="BU6" t="s">
         <v>116</v>
       </c>
-      <c r="BU6" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="7" spans="6:73">
-      <c r="AC7" t="s">
-        <v>332</v>
-      </c>
+      <c r="BV6" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="7" spans="7:74">
       <c r="AD7" t="s">
-        <v>344</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>402</v>
-      </c>
-      <c r="BA7" t="s">
-        <v>701</v>
-      </c>
-      <c r="BU7" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="8" spans="6:73">
-      <c r="AC8" t="s">
-        <v>333</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>346</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>404</v>
+      </c>
+      <c r="BB7" t="s">
+        <v>703</v>
+      </c>
+      <c r="BV7" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="8" spans="7:74">
       <c r="AD8" t="s">
-        <v>345</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>403</v>
-      </c>
-      <c r="BU8" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="9" spans="6:73">
-      <c r="AC9" t="s">
-        <v>334</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>347</v>
+      </c>
+      <c r="AY8" t="s">
+        <v>405</v>
+      </c>
+      <c r="BV8" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="9" spans="7:74">
       <c r="AD9" t="s">
-        <v>346</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>404</v>
-      </c>
-      <c r="BU9" t="s">
+        <v>336</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>348</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>406</v>
+      </c>
+      <c r="BV9" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="10" spans="6:73">
-      <c r="AC10" t="s">
-        <v>335</v>
-      </c>
+    <row r="10" spans="7:74">
       <c r="AD10" t="s">
-        <v>347</v>
-      </c>
-      <c r="AX10" t="s">
-        <v>405</v>
-      </c>
-      <c r="BU10" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="11" spans="6:73">
-      <c r="AX11" t="s">
-        <v>406</v>
-      </c>
-      <c r="BU11" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="12" spans="6:73">
-      <c r="AX12" t="s">
+        <v>337</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>349</v>
+      </c>
+      <c r="AY10" t="s">
         <v>407</v>
       </c>
-      <c r="BU12" t="s">
+      <c r="BV10" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="13" spans="6:73">
-      <c r="AX13" t="s">
+    <row r="11" spans="7:74">
+      <c r="AY11" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="14" spans="6:73">
-      <c r="AX14" t="s">
+      <c r="BV11" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="12" spans="7:74">
+      <c r="AY12" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="15" spans="6:73">
-      <c r="AX15" t="s">
+      <c r="BV12" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="13" spans="7:74">
+      <c r="AY13" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="16" spans="6:73">
-      <c r="AX16" t="s">
+    <row r="14" spans="7:74">
+      <c r="AY14" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="17" spans="50:50">
-      <c r="AX17" t="s">
+    <row r="15" spans="7:74">
+      <c r="AY15" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="18" spans="50:50">
-      <c r="AX18" t="s">
+    <row r="16" spans="7:74">
+      <c r="AY16" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="19" spans="50:50">
-      <c r="AX19" t="s">
+    <row r="17" spans="51:51">
+      <c r="AY17" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="20" spans="50:50">
-      <c r="AX20" t="s">
+    <row r="18" spans="51:51">
+      <c r="AY18" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="21" spans="50:50">
-      <c r="AX21" t="s">
+    <row r="19" spans="51:51">
+      <c r="AY19" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="22" spans="50:50">
-      <c r="AX22" t="s">
+    <row r="20" spans="51:51">
+      <c r="AY20" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="23" spans="50:50">
-      <c r="AX23" t="s">
+    <row r="21" spans="51:51">
+      <c r="AY21" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="24" spans="50:50">
-      <c r="AX24" t="s">
+    <row r="22" spans="51:51">
+      <c r="AY22" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="25" spans="50:50">
-      <c r="AX25" t="s">
+    <row r="23" spans="51:51">
+      <c r="AY23" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="26" spans="50:50">
-      <c r="AX26" t="s">
+    <row r="24" spans="51:51">
+      <c r="AY24" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="27" spans="50:50">
-      <c r="AX27" t="s">
+    <row r="25" spans="51:51">
+      <c r="AY25" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="28" spans="50:50">
-      <c r="AX28" t="s">
+    <row r="26" spans="51:51">
+      <c r="AY26" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="29" spans="50:50">
-      <c r="AX29" t="s">
+    <row r="27" spans="51:51">
+      <c r="AY27" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="30" spans="50:50">
-      <c r="AX30" t="s">
+    <row r="28" spans="51:51">
+      <c r="AY28" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="31" spans="50:50">
-      <c r="AX31" t="s">
+    <row r="29" spans="51:51">
+      <c r="AY29" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="32" spans="50:50">
-      <c r="AX32" t="s">
+    <row r="30" spans="51:51">
+      <c r="AY30" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="33" spans="50:50">
-      <c r="AX33" t="s">
+    <row r="31" spans="51:51">
+      <c r="AY31" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="34" spans="50:50">
-      <c r="AX34" t="s">
+    <row r="32" spans="51:51">
+      <c r="AY32" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="35" spans="50:50">
-      <c r="AX35" t="s">
+    <row r="33" spans="51:51">
+      <c r="AY33" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="36" spans="50:50">
-      <c r="AX36" t="s">
+    <row r="34" spans="51:51">
+      <c r="AY34" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="37" spans="50:50">
-      <c r="AX37" t="s">
+    <row r="35" spans="51:51">
+      <c r="AY35" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="38" spans="50:50">
-      <c r="AX38" t="s">
+    <row r="36" spans="51:51">
+      <c r="AY36" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="39" spans="50:50">
-      <c r="AX39" t="s">
+    <row r="37" spans="51:51">
+      <c r="AY37" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="40" spans="50:50">
-      <c r="AX40" t="s">
+    <row r="38" spans="51:51">
+      <c r="AY38" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="41" spans="50:50">
-      <c r="AX41" t="s">
+    <row r="39" spans="51:51">
+      <c r="AY39" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="42" spans="50:50">
-      <c r="AX42" t="s">
+    <row r="40" spans="51:51">
+      <c r="AY40" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="43" spans="50:50">
-      <c r="AX43" t="s">
+    <row r="41" spans="51:51">
+      <c r="AY41" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="44" spans="50:50">
-      <c r="AX44" t="s">
+    <row r="42" spans="51:51">
+      <c r="AY42" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="45" spans="50:50">
-      <c r="AX45" t="s">
+    <row r="43" spans="51:51">
+      <c r="AY43" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="46" spans="50:50">
-      <c r="AX46" t="s">
+    <row r="44" spans="51:51">
+      <c r="AY44" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="47" spans="50:50">
-      <c r="AX47" t="s">
+    <row r="45" spans="51:51">
+      <c r="AY45" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="48" spans="50:50">
-      <c r="AX48" t="s">
+    <row r="46" spans="51:51">
+      <c r="AY46" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="49" spans="50:50">
-      <c r="AX49" t="s">
+    <row r="47" spans="51:51">
+      <c r="AY47" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="50" spans="50:50">
-      <c r="AX50" t="s">
+    <row r="48" spans="51:51">
+      <c r="AY48" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="51" spans="50:50">
-      <c r="AX51" t="s">
+    <row r="49" spans="51:51">
+      <c r="AY49" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="52" spans="50:50">
-      <c r="AX52" t="s">
+    <row r="50" spans="51:51">
+      <c r="AY50" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="53" spans="50:50">
-      <c r="AX53" t="s">
+    <row r="51" spans="51:51">
+      <c r="AY51" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="54" spans="50:50">
-      <c r="AX54" t="s">
+    <row r="52" spans="51:51">
+      <c r="AY52" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="55" spans="50:50">
-      <c r="AX55" t="s">
+    <row r="53" spans="51:51">
+      <c r="AY53" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="56" spans="50:50">
-      <c r="AX56" t="s">
+    <row r="54" spans="51:51">
+      <c r="AY54" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="57" spans="50:50">
-      <c r="AX57" t="s">
+    <row r="55" spans="51:51">
+      <c r="AY55" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="58" spans="50:50">
-      <c r="AX58" t="s">
+    <row r="56" spans="51:51">
+      <c r="AY56" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="59" spans="50:50">
-      <c r="AX59" t="s">
+    <row r="57" spans="51:51">
+      <c r="AY57" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="60" spans="50:50">
-      <c r="AX60" t="s">
+    <row r="58" spans="51:51">
+      <c r="AY58" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="61" spans="50:50">
-      <c r="AX61" t="s">
+    <row r="59" spans="51:51">
+      <c r="AY59" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="62" spans="50:50">
-      <c r="AX62" t="s">
+    <row r="60" spans="51:51">
+      <c r="AY60" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="63" spans="50:50">
-      <c r="AX63" t="s">
+    <row r="61" spans="51:51">
+      <c r="AY61" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="64" spans="50:50">
-      <c r="AX64" t="s">
+    <row r="62" spans="51:51">
+      <c r="AY62" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="65" spans="50:50">
-      <c r="AX65" t="s">
+    <row r="63" spans="51:51">
+      <c r="AY63" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="66" spans="50:50">
-      <c r="AX66" t="s">
+    <row r="64" spans="51:51">
+      <c r="AY64" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="67" spans="50:50">
-      <c r="AX67" t="s">
+    <row r="65" spans="51:51">
+      <c r="AY65" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="68" spans="50:50">
-      <c r="AX68" t="s">
+    <row r="66" spans="51:51">
+      <c r="AY66" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="69" spans="50:50">
-      <c r="AX69" t="s">
+    <row r="67" spans="51:51">
+      <c r="AY67" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="70" spans="50:50">
-      <c r="AX70" t="s">
+    <row r="68" spans="51:51">
+      <c r="AY68" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="71" spans="50:50">
-      <c r="AX71" t="s">
+    <row r="69" spans="51:51">
+      <c r="AY69" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="72" spans="50:50">
-      <c r="AX72" t="s">
+    <row r="70" spans="51:51">
+      <c r="AY70" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="73" spans="50:50">
-      <c r="AX73" t="s">
+    <row r="71" spans="51:51">
+      <c r="AY71" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="74" spans="50:50">
-      <c r="AX74" t="s">
+    <row r="72" spans="51:51">
+      <c r="AY72" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="75" spans="50:50">
-      <c r="AX75" t="s">
+    <row r="73" spans="51:51">
+      <c r="AY73" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="76" spans="50:50">
-      <c r="AX76" t="s">
+    <row r="74" spans="51:51">
+      <c r="AY74" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="77" spans="50:50">
-      <c r="AX77" t="s">
+    <row r="75" spans="51:51">
+      <c r="AY75" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="78" spans="50:50">
-      <c r="AX78" t="s">
+    <row r="76" spans="51:51">
+      <c r="AY76" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="79" spans="50:50">
-      <c r="AX79" t="s">
+    <row r="77" spans="51:51">
+      <c r="AY77" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="80" spans="50:50">
-      <c r="AX80" t="s">
+    <row r="78" spans="51:51">
+      <c r="AY78" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="81" spans="50:50">
-      <c r="AX81" t="s">
+    <row r="79" spans="51:51">
+      <c r="AY79" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="82" spans="50:50">
-      <c r="AX82" t="s">
+    <row r="80" spans="51:51">
+      <c r="AY80" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="83" spans="50:50">
-      <c r="AX83" t="s">
+    <row r="81" spans="51:51">
+      <c r="AY81" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="84" spans="50:50">
-      <c r="AX84" t="s">
+    <row r="82" spans="51:51">
+      <c r="AY82" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="85" spans="50:50">
-      <c r="AX85" t="s">
+    <row r="83" spans="51:51">
+      <c r="AY83" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="86" spans="50:50">
-      <c r="AX86" t="s">
+    <row r="84" spans="51:51">
+      <c r="AY84" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="87" spans="50:50">
-      <c r="AX87" t="s">
+    <row r="85" spans="51:51">
+      <c r="AY85" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="88" spans="50:50">
-      <c r="AX88" t="s">
+    <row r="86" spans="51:51">
+      <c r="AY86" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="89" spans="50:50">
-      <c r="AX89" t="s">
+    <row r="87" spans="51:51">
+      <c r="AY87" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="90" spans="50:50">
-      <c r="AX90" t="s">
+    <row r="88" spans="51:51">
+      <c r="AY88" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="91" spans="50:50">
-      <c r="AX91" t="s">
+    <row r="89" spans="51:51">
+      <c r="AY89" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="92" spans="50:50">
-      <c r="AX92" t="s">
+    <row r="90" spans="51:51">
+      <c r="AY90" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="93" spans="50:50">
-      <c r="AX93" t="s">
+    <row r="91" spans="51:51">
+      <c r="AY91" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="94" spans="50:50">
-      <c r="AX94" t="s">
+    <row r="92" spans="51:51">
+      <c r="AY92" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="95" spans="50:50">
-      <c r="AX95" t="s">
+    <row r="93" spans="51:51">
+      <c r="AY93" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="96" spans="50:50">
-      <c r="AX96" t="s">
+    <row r="94" spans="51:51">
+      <c r="AY94" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="97" spans="50:50">
-      <c r="AX97" t="s">
+    <row r="95" spans="51:51">
+      <c r="AY95" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="98" spans="50:50">
-      <c r="AX98" t="s">
+    <row r="96" spans="51:51">
+      <c r="AY96" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="99" spans="50:50">
-      <c r="AX99" t="s">
+    <row r="97" spans="51:51">
+      <c r="AY97" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="100" spans="50:50">
-      <c r="AX100" t="s">
+    <row r="98" spans="51:51">
+      <c r="AY98" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="101" spans="50:50">
-      <c r="AX101" t="s">
+    <row r="99" spans="51:51">
+      <c r="AY99" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="102" spans="50:50">
-      <c r="AX102" t="s">
+    <row r="100" spans="51:51">
+      <c r="AY100" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="103" spans="50:50">
-      <c r="AX103" t="s">
+    <row r="101" spans="51:51">
+      <c r="AY101" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="104" spans="50:50">
-      <c r="AX104" t="s">
+    <row r="102" spans="51:51">
+      <c r="AY102" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="105" spans="50:50">
-      <c r="AX105" t="s">
+    <row r="103" spans="51:51">
+      <c r="AY103" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="106" spans="50:50">
-      <c r="AX106" t="s">
+    <row r="104" spans="51:51">
+      <c r="AY104" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="107" spans="50:50">
-      <c r="AX107" t="s">
+    <row r="105" spans="51:51">
+      <c r="AY105" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="108" spans="50:50">
-      <c r="AX108" t="s">
+    <row r="106" spans="51:51">
+      <c r="AY106" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="109" spans="50:50">
-      <c r="AX109" t="s">
+    <row r="107" spans="51:51">
+      <c r="AY107" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="110" spans="50:50">
-      <c r="AX110" t="s">
+    <row r="108" spans="51:51">
+      <c r="AY108" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="111" spans="50:50">
-      <c r="AX111" t="s">
+    <row r="109" spans="51:51">
+      <c r="AY109" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="112" spans="50:50">
-      <c r="AX112" t="s">
+    <row r="110" spans="51:51">
+      <c r="AY110" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="113" spans="50:50">
-      <c r="AX113" t="s">
+    <row r="111" spans="51:51">
+      <c r="AY111" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="114" spans="50:50">
-      <c r="AX114" t="s">
+    <row r="112" spans="51:51">
+      <c r="AY112" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="115" spans="50:50">
-      <c r="AX115" t="s">
+    <row r="113" spans="51:51">
+      <c r="AY113" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="116" spans="50:50">
-      <c r="AX116" t="s">
+    <row r="114" spans="51:51">
+      <c r="AY114" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="117" spans="50:50">
-      <c r="AX117" t="s">
+    <row r="115" spans="51:51">
+      <c r="AY115" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="118" spans="50:50">
-      <c r="AX118" t="s">
+    <row r="116" spans="51:51">
+      <c r="AY116" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="119" spans="50:50">
-      <c r="AX119" t="s">
+    <row r="117" spans="51:51">
+      <c r="AY117" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="120" spans="50:50">
-      <c r="AX120" t="s">
+    <row r="118" spans="51:51">
+      <c r="AY118" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="121" spans="50:50">
-      <c r="AX121" t="s">
+    <row r="119" spans="51:51">
+      <c r="AY119" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="122" spans="50:50">
-      <c r="AX122" t="s">
+    <row r="120" spans="51:51">
+      <c r="AY120" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="123" spans="50:50">
-      <c r="AX123" t="s">
+    <row r="121" spans="51:51">
+      <c r="AY121" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="124" spans="50:50">
-      <c r="AX124" t="s">
+    <row r="122" spans="51:51">
+      <c r="AY122" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="125" spans="50:50">
-      <c r="AX125" t="s">
+    <row r="123" spans="51:51">
+      <c r="AY123" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="126" spans="50:50">
-      <c r="AX126" t="s">
+    <row r="124" spans="51:51">
+      <c r="AY124" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="127" spans="50:50">
-      <c r="AX127" t="s">
+    <row r="125" spans="51:51">
+      <c r="AY125" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="128" spans="50:50">
-      <c r="AX128" t="s">
+    <row r="126" spans="51:51">
+      <c r="AY126" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="129" spans="50:50">
-      <c r="AX129" t="s">
+    <row r="127" spans="51:51">
+      <c r="AY127" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="130" spans="50:50">
-      <c r="AX130" t="s">
+    <row r="128" spans="51:51">
+      <c r="AY128" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="131" spans="50:50">
-      <c r="AX131" t="s">
+    <row r="129" spans="51:51">
+      <c r="AY129" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="132" spans="50:50">
-      <c r="AX132" t="s">
+    <row r="130" spans="51:51">
+      <c r="AY130" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="133" spans="50:50">
-      <c r="AX133" t="s">
+    <row r="131" spans="51:51">
+      <c r="AY131" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="134" spans="50:50">
-      <c r="AX134" t="s">
+    <row r="132" spans="51:51">
+      <c r="AY132" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="135" spans="50:50">
-      <c r="AX135" t="s">
+    <row r="133" spans="51:51">
+      <c r="AY133" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="136" spans="50:50">
-      <c r="AX136" t="s">
+    <row r="134" spans="51:51">
+      <c r="AY134" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="137" spans="50:50">
-      <c r="AX137" t="s">
+    <row r="135" spans="51:51">
+      <c r="AY135" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="138" spans="50:50">
-      <c r="AX138" t="s">
+    <row r="136" spans="51:51">
+      <c r="AY136" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="139" spans="50:50">
-      <c r="AX139" t="s">
+    <row r="137" spans="51:51">
+      <c r="AY137" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="140" spans="50:50">
-      <c r="AX140" t="s">
+    <row r="138" spans="51:51">
+      <c r="AY138" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="141" spans="50:50">
-      <c r="AX141" t="s">
+    <row r="139" spans="51:51">
+      <c r="AY139" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="142" spans="50:50">
-      <c r="AX142" t="s">
+    <row r="140" spans="51:51">
+      <c r="AY140" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="143" spans="50:50">
-      <c r="AX143" t="s">
+    <row r="141" spans="51:51">
+      <c r="AY141" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="144" spans="50:50">
-      <c r="AX144" t="s">
+    <row r="142" spans="51:51">
+      <c r="AY142" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="145" spans="50:50">
-      <c r="AX145" t="s">
+    <row r="143" spans="51:51">
+      <c r="AY143" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="146" spans="50:50">
-      <c r="AX146" t="s">
+    <row r="144" spans="51:51">
+      <c r="AY144" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="147" spans="50:50">
-      <c r="AX147" t="s">
+    <row r="145" spans="51:51">
+      <c r="AY145" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="148" spans="50:50">
-      <c r="AX148" t="s">
+    <row r="146" spans="51:51">
+      <c r="AY146" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="149" spans="50:50">
-      <c r="AX149" t="s">
+    <row r="147" spans="51:51">
+      <c r="AY147" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="150" spans="50:50">
-      <c r="AX150" t="s">
+    <row r="148" spans="51:51">
+      <c r="AY148" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="151" spans="50:50">
-      <c r="AX151" t="s">
+    <row r="149" spans="51:51">
+      <c r="AY149" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="152" spans="50:50">
-      <c r="AX152" t="s">
+    <row r="150" spans="51:51">
+      <c r="AY150" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="153" spans="50:50">
-      <c r="AX153" t="s">
+    <row r="151" spans="51:51">
+      <c r="AY151" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="154" spans="50:50">
-      <c r="AX154" t="s">
+    <row r="152" spans="51:51">
+      <c r="AY152" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="155" spans="50:50">
-      <c r="AX155" t="s">
+    <row r="153" spans="51:51">
+      <c r="AY153" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="156" spans="50:50">
-      <c r="AX156" t="s">
+    <row r="154" spans="51:51">
+      <c r="AY154" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="157" spans="50:50">
-      <c r="AX157" t="s">
+    <row r="155" spans="51:51">
+      <c r="AY155" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="158" spans="50:50">
-      <c r="AX158" t="s">
+    <row r="156" spans="51:51">
+      <c r="AY156" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="159" spans="50:50">
-      <c r="AX159" t="s">
+    <row r="157" spans="51:51">
+      <c r="AY157" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="160" spans="50:50">
-      <c r="AX160" t="s">
+    <row r="158" spans="51:51">
+      <c r="AY158" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="161" spans="50:50">
-      <c r="AX161" t="s">
+    <row r="159" spans="51:51">
+      <c r="AY159" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="162" spans="50:50">
-      <c r="AX162" t="s">
+    <row r="160" spans="51:51">
+      <c r="AY160" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="163" spans="50:50">
-      <c r="AX163" t="s">
+    <row r="161" spans="51:51">
+      <c r="AY161" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="164" spans="50:50">
-      <c r="AX164" t="s">
+    <row r="162" spans="51:51">
+      <c r="AY162" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="165" spans="50:50">
-      <c r="AX165" t="s">
+    <row r="163" spans="51:51">
+      <c r="AY163" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="166" spans="50:50">
-      <c r="AX166" t="s">
+    <row r="164" spans="51:51">
+      <c r="AY164" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="167" spans="50:50">
-      <c r="AX167" t="s">
+    <row r="165" spans="51:51">
+      <c r="AY165" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="168" spans="50:50">
-      <c r="AX168" t="s">
+    <row r="166" spans="51:51">
+      <c r="AY166" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="169" spans="50:50">
-      <c r="AX169" t="s">
+    <row r="167" spans="51:51">
+      <c r="AY167" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="170" spans="50:50">
-      <c r="AX170" t="s">
+    <row r="168" spans="51:51">
+      <c r="AY168" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="171" spans="50:50">
-      <c r="AX171" t="s">
+    <row r="169" spans="51:51">
+      <c r="AY169" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="172" spans="50:50">
-      <c r="AX172" t="s">
+    <row r="170" spans="51:51">
+      <c r="AY170" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="173" spans="50:50">
-      <c r="AX173" t="s">
+    <row r="171" spans="51:51">
+      <c r="AY171" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="174" spans="50:50">
-      <c r="AX174" t="s">
+    <row r="172" spans="51:51">
+      <c r="AY172" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="175" spans="50:50">
-      <c r="AX175" t="s">
+    <row r="173" spans="51:51">
+      <c r="AY173" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="176" spans="50:50">
-      <c r="AX176" t="s">
+    <row r="174" spans="51:51">
+      <c r="AY174" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="177" spans="50:50">
-      <c r="AX177" t="s">
+    <row r="175" spans="51:51">
+      <c r="AY175" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="178" spans="50:50">
-      <c r="AX178" t="s">
+    <row r="176" spans="51:51">
+      <c r="AY176" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="179" spans="50:50">
-      <c r="AX179" t="s">
+    <row r="177" spans="51:51">
+      <c r="AY177" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="180" spans="50:50">
-      <c r="AX180" t="s">
+    <row r="178" spans="51:51">
+      <c r="AY178" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="181" spans="50:50">
-      <c r="AX181" t="s">
+    <row r="179" spans="51:51">
+      <c r="AY179" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="182" spans="50:50">
-      <c r="AX182" t="s">
+    <row r="180" spans="51:51">
+      <c r="AY180" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="183" spans="50:50">
-      <c r="AX183" t="s">
+    <row r="181" spans="51:51">
+      <c r="AY181" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="184" spans="50:50">
-      <c r="AX184" t="s">
+    <row r="182" spans="51:51">
+      <c r="AY182" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="185" spans="50:50">
-      <c r="AX185" t="s">
+    <row r="183" spans="51:51">
+      <c r="AY183" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="186" spans="50:50">
-      <c r="AX186" t="s">
+    <row r="184" spans="51:51">
+      <c r="AY184" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="187" spans="50:50">
-      <c r="AX187" t="s">
+    <row r="185" spans="51:51">
+      <c r="AY185" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="188" spans="50:50">
-      <c r="AX188" t="s">
+    <row r="186" spans="51:51">
+      <c r="AY186" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="189" spans="50:50">
-      <c r="AX189" t="s">
+    <row r="187" spans="51:51">
+      <c r="AY187" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="190" spans="50:50">
-      <c r="AX190" t="s">
+    <row r="188" spans="51:51">
+      <c r="AY188" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="191" spans="50:50">
-      <c r="AX191" t="s">
+    <row r="189" spans="51:51">
+      <c r="AY189" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="192" spans="50:50">
-      <c r="AX192" t="s">
+    <row r="190" spans="51:51">
+      <c r="AY190" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="193" spans="50:50">
-      <c r="AX193" t="s">
+    <row r="191" spans="51:51">
+      <c r="AY191" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="194" spans="50:50">
-      <c r="AX194" t="s">
+    <row r="192" spans="51:51">
+      <c r="AY192" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="195" spans="50:50">
-      <c r="AX195" t="s">
+    <row r="193" spans="51:51">
+      <c r="AY193" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="196" spans="50:50">
-      <c r="AX196" t="s">
+    <row r="194" spans="51:51">
+      <c r="AY194" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="197" spans="50:50">
-      <c r="AX197" t="s">
+    <row r="195" spans="51:51">
+      <c r="AY195" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="198" spans="50:50">
-      <c r="AX198" t="s">
+    <row r="196" spans="51:51">
+      <c r="AY196" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="199" spans="50:50">
-      <c r="AX199" t="s">
+    <row r="197" spans="51:51">
+      <c r="AY197" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="200" spans="50:50">
-      <c r="AX200" t="s">
+    <row r="198" spans="51:51">
+      <c r="AY198" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="201" spans="50:50">
-      <c r="AX201" t="s">
+    <row r="199" spans="51:51">
+      <c r="AY199" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="202" spans="50:50">
-      <c r="AX202" t="s">
+    <row r="200" spans="51:51">
+      <c r="AY200" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="203" spans="50:50">
-      <c r="AX203" t="s">
+    <row r="201" spans="51:51">
+      <c r="AY201" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="204" spans="50:50">
-      <c r="AX204" t="s">
+    <row r="202" spans="51:51">
+      <c r="AY202" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="205" spans="50:50">
-      <c r="AX205" t="s">
+    <row r="203" spans="51:51">
+      <c r="AY203" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="206" spans="50:50">
-      <c r="AX206" t="s">
+    <row r="204" spans="51:51">
+      <c r="AY204" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="207" spans="50:50">
-      <c r="AX207" t="s">
+    <row r="205" spans="51:51">
+      <c r="AY205" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="208" spans="50:50">
-      <c r="AX208" t="s">
+    <row r="206" spans="51:51">
+      <c r="AY206" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="209" spans="50:50">
-      <c r="AX209" t="s">
+    <row r="207" spans="51:51">
+      <c r="AY207" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="210" spans="50:50">
-      <c r="AX210" t="s">
+    <row r="208" spans="51:51">
+      <c r="AY208" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="211" spans="50:50">
-      <c r="AX211" t="s">
+    <row r="209" spans="51:51">
+      <c r="AY209" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="212" spans="50:50">
-      <c r="AX212" t="s">
+    <row r="210" spans="51:51">
+      <c r="AY210" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="213" spans="50:50">
-      <c r="AX213" t="s">
+    <row r="211" spans="51:51">
+      <c r="AY211" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="214" spans="50:50">
-      <c r="AX214" t="s">
+    <row r="212" spans="51:51">
+      <c r="AY212" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="215" spans="50:50">
-      <c r="AX215" t="s">
+    <row r="213" spans="51:51">
+      <c r="AY213" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="216" spans="50:50">
-      <c r="AX216" t="s">
+    <row r="214" spans="51:51">
+      <c r="AY214" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="217" spans="50:50">
-      <c r="AX217" t="s">
+    <row r="215" spans="51:51">
+      <c r="AY215" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="218" spans="50:50">
-      <c r="AX218" t="s">
+    <row r="216" spans="51:51">
+      <c r="AY216" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="219" spans="50:50">
-      <c r="AX219" t="s">
+    <row r="217" spans="51:51">
+      <c r="AY217" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="220" spans="50:50">
-      <c r="AX220" t="s">
+    <row r="218" spans="51:51">
+      <c r="AY218" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="221" spans="50:50">
-      <c r="AX221" t="s">
+    <row r="219" spans="51:51">
+      <c r="AY219" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="222" spans="50:50">
-      <c r="AX222" t="s">
+    <row r="220" spans="51:51">
+      <c r="AY220" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="223" spans="50:50">
-      <c r="AX223" t="s">
+    <row r="221" spans="51:51">
+      <c r="AY221" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="224" spans="50:50">
-      <c r="AX224" t="s">
+    <row r="222" spans="51:51">
+      <c r="AY222" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="225" spans="50:50">
-      <c r="AX225" t="s">
+    <row r="223" spans="51:51">
+      <c r="AY223" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="226" spans="50:50">
-      <c r="AX226" t="s">
+    <row r="224" spans="51:51">
+      <c r="AY224" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="227" spans="50:50">
-      <c r="AX227" t="s">
+    <row r="225" spans="51:51">
+      <c r="AY225" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="228" spans="50:50">
-      <c r="AX228" t="s">
+    <row r="226" spans="51:51">
+      <c r="AY226" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="229" spans="50:50">
-      <c r="AX229" t="s">
+    <row r="227" spans="51:51">
+      <c r="AY227" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="230" spans="50:50">
-      <c r="AX230" t="s">
+    <row r="228" spans="51:51">
+      <c r="AY228" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="231" spans="50:50">
-      <c r="AX231" t="s">
+    <row r="229" spans="51:51">
+      <c r="AY229" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="232" spans="50:50">
-      <c r="AX232" t="s">
+    <row r="230" spans="51:51">
+      <c r="AY230" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="233" spans="50:50">
-      <c r="AX233" t="s">
+    <row r="231" spans="51:51">
+      <c r="AY231" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="234" spans="50:50">
-      <c r="AX234" t="s">
+    <row r="232" spans="51:51">
+      <c r="AY232" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="235" spans="50:50">
-      <c r="AX235" t="s">
+    <row r="233" spans="51:51">
+      <c r="AY233" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="236" spans="50:50">
-      <c r="AX236" t="s">
+    <row r="234" spans="51:51">
+      <c r="AY234" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="237" spans="50:50">
-      <c r="AX237" t="s">
+    <row r="235" spans="51:51">
+      <c r="AY235" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="238" spans="50:50">
-      <c r="AX238" t="s">
+    <row r="236" spans="51:51">
+      <c r="AY236" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="239" spans="50:50">
-      <c r="AX239" t="s">
+    <row r="237" spans="51:51">
+      <c r="AY237" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="240" spans="50:50">
-      <c r="AX240" t="s">
+    <row r="238" spans="51:51">
+      <c r="AY238" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="241" spans="50:50">
-      <c r="AX241" t="s">
+    <row r="239" spans="51:51">
+      <c r="AY239" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="242" spans="50:50">
-      <c r="AX242" t="s">
+    <row r="240" spans="51:51">
+      <c r="AY240" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="243" spans="50:50">
-      <c r="AX243" t="s">
+    <row r="241" spans="51:51">
+      <c r="AY241" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="244" spans="50:50">
-      <c r="AX244" t="s">
+    <row r="242" spans="51:51">
+      <c r="AY242" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="245" spans="50:50">
-      <c r="AX245" t="s">
+    <row r="243" spans="51:51">
+      <c r="AY243" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="246" spans="50:50">
-      <c r="AX246" t="s">
+    <row r="244" spans="51:51">
+      <c r="AY244" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="247" spans="50:50">
-      <c r="AX247" t="s">
+    <row r="245" spans="51:51">
+      <c r="AY245" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="248" spans="50:50">
-      <c r="AX248" t="s">
+    <row r="246" spans="51:51">
+      <c r="AY246" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="249" spans="50:50">
-      <c r="AX249" t="s">
+    <row r="247" spans="51:51">
+      <c r="AY247" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="250" spans="50:50">
-      <c r="AX250" t="s">
+    <row r="248" spans="51:51">
+      <c r="AY248" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="251" spans="50:50">
-      <c r="AX251" t="s">
+    <row r="249" spans="51:51">
+      <c r="AY249" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="252" spans="50:50">
-      <c r="AX252" t="s">
+    <row r="250" spans="51:51">
+      <c r="AY250" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="253" spans="50:50">
-      <c r="AX253" t="s">
+    <row r="251" spans="51:51">
+      <c r="AY251" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="254" spans="50:50">
-      <c r="AX254" t="s">
+    <row r="252" spans="51:51">
+      <c r="AY252" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="255" spans="50:50">
-      <c r="AX255" t="s">
+    <row r="253" spans="51:51">
+      <c r="AY253" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="256" spans="50:50">
-      <c r="AX256" t="s">
+    <row r="254" spans="51:51">
+      <c r="AY254" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="257" spans="50:50">
-      <c r="AX257" t="s">
+    <row r="255" spans="51:51">
+      <c r="AY255" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="258" spans="50:50">
-      <c r="AX258" t="s">
+    <row r="256" spans="51:51">
+      <c r="AY256" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="259" spans="50:50">
-      <c r="AX259" t="s">
+    <row r="257" spans="51:51">
+      <c r="AY257" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="260" spans="50:50">
-      <c r="AX260" t="s">
+    <row r="258" spans="51:51">
+      <c r="AY258" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="261" spans="50:50">
-      <c r="AX261" t="s">
+    <row r="259" spans="51:51">
+      <c r="AY259" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="262" spans="50:50">
-      <c r="AX262" t="s">
+    <row r="260" spans="51:51">
+      <c r="AY260" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="263" spans="50:50">
-      <c r="AX263" t="s">
+    <row r="261" spans="51:51">
+      <c r="AY261" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="264" spans="50:50">
-      <c r="AX264" t="s">
+    <row r="262" spans="51:51">
+      <c r="AY262" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="265" spans="50:50">
-      <c r="AX265" t="s">
+    <row r="263" spans="51:51">
+      <c r="AY263" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="266" spans="50:50">
-      <c r="AX266" t="s">
+    <row r="264" spans="51:51">
+      <c r="AY264" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="267" spans="50:50">
-      <c r="AX267" t="s">
+    <row r="265" spans="51:51">
+      <c r="AY265" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="268" spans="50:50">
-      <c r="AX268" t="s">
+    <row r="266" spans="51:51">
+      <c r="AY266" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="269" spans="50:50">
-      <c r="AX269" t="s">
+    <row r="267" spans="51:51">
+      <c r="AY267" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="270" spans="50:50">
-      <c r="AX270" t="s">
+    <row r="268" spans="51:51">
+      <c r="AY268" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="271" spans="50:50">
-      <c r="AX271" t="s">
+    <row r="269" spans="51:51">
+      <c r="AY269" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="272" spans="50:50">
-      <c r="AX272" t="s">
+    <row r="270" spans="51:51">
+      <c r="AY270" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="273" spans="50:50">
-      <c r="AX273" t="s">
+    <row r="271" spans="51:51">
+      <c r="AY271" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="274" spans="50:50">
-      <c r="AX274" t="s">
+    <row r="272" spans="51:51">
+      <c r="AY272" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="275" spans="50:50">
-      <c r="AX275" t="s">
+    <row r="273" spans="51:51">
+      <c r="AY273" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="276" spans="50:50">
-      <c r="AX276" t="s">
+    <row r="274" spans="51:51">
+      <c r="AY274" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="277" spans="50:50">
-      <c r="AX277" t="s">
+    <row r="275" spans="51:51">
+      <c r="AY275" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="278" spans="50:50">
-      <c r="AX278" t="s">
+    <row r="276" spans="51:51">
+      <c r="AY276" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="279" spans="50:50">
-      <c r="AX279" t="s">
+    <row r="277" spans="51:51">
+      <c r="AY277" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="280" spans="50:50">
-      <c r="AX280" t="s">
+    <row r="278" spans="51:51">
+      <c r="AY278" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="281" spans="50:50">
-      <c r="AX281" t="s">
+    <row r="279" spans="51:51">
+      <c r="AY279" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="282" spans="50:50">
-      <c r="AX282" t="s">
+    <row r="280" spans="51:51">
+      <c r="AY280" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="283" spans="50:50">
-      <c r="AX283" t="s">
+    <row r="281" spans="51:51">
+      <c r="AY281" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="284" spans="50:50">
-      <c r="AX284" t="s">
+    <row r="282" spans="51:51">
+      <c r="AY282" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="285" spans="50:50">
-      <c r="AX285" t="s">
+    <row r="283" spans="51:51">
+      <c r="AY283" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="286" spans="50:50">
-      <c r="AX286" t="s">
+    <row r="284" spans="51:51">
+      <c r="AY284" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="287" spans="50:50">
-      <c r="AX287" t="s">
+    <row r="285" spans="51:51">
+      <c r="AY285" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="288" spans="50:50">
-      <c r="AX288" t="s">
+    <row r="286" spans="51:51">
+      <c r="AY286" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="289" spans="50:50">
-      <c r="AX289" t="s">
+    <row r="287" spans="51:51">
+      <c r="AY287" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="290" spans="50:50">
-      <c r="AX290" t="s">
+    <row r="288" spans="51:51">
+      <c r="AY288" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="291" spans="50:50">
-      <c r="AX291" t="s">
+    <row r="289" spans="51:51">
+      <c r="AY289" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="292" spans="50:50">
-      <c r="AX292" t="s">
+    <row r="290" spans="51:51">
+      <c r="AY290" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="293" spans="50:50">
-      <c r="AX293" t="s">
+    <row r="291" spans="51:51">
+      <c r="AY291" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="294" spans="50:50">
-      <c r="AX294" t="s">
+    <row r="292" spans="51:51">
+      <c r="AY292" t="s">
         <v>689</v>
+      </c>
+    </row>
+    <row r="293" spans="51:51">
+      <c r="AY293" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="294" spans="51:51">
+      <c r="AY294" t="s">
+        <v>691</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000049/metadata_template_ERC000049.xlsx
+++ b/templates/ERC000049/metadata_template_ERC000049.xlsx
@@ -19,14 +19,14 @@
   <definedNames>
     <definedName name="detectiontype">'cv_sample'!$AG$1:$AG$2</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AY$1:$AY$289</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AY$1:$AY$294</definedName>
     <definedName name="hostpredictionapproach">'cv_sample'!$BB$1:$BB$7</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="observedbioticrelationship">'cv_sample'!$G$1:$G$5</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="predictedgenomestructure">'cv_sample'!$AF$1:$AF$3</definedName>
     <definedName name="predictedgenometype">'cv_sample'!$AE$1:$AE$10</definedName>
     <definedName name="reassemblypostbinning">'cv_sample'!$Z$1:$Z$2</definedName>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="771">
   <si>
     <t>alias</t>
   </si>
@@ -459,6 +459,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -549,6 +552,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1446,9 +1452,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1467,6 +1470,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1668,6 +1674,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1677,9 +1686,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1719,7 +1725,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1788,6 +1794,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1863,6 +1872,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1884,6 +1896,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1929,6 +1944,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1941,6 +1959,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1950,9 +1971,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1977,6 +1995,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2037,10 +2058,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -2861,10 +2882,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2905,10 +2926,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2935,7 +2956,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -2952,7 +2973,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -2969,7 +2990,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -2986,7 +3007,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -3003,7 +3024,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -3020,7 +3041,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -3037,7 +3058,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -3054,7 +3075,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -3071,7 +3092,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -3088,7 +3109,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -3102,7 +3123,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -3116,7 +3137,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -3130,7 +3151,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -3144,7 +3165,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -3158,7 +3179,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -3172,7 +3193,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -3186,7 +3207,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -3200,7 +3221,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -3210,8 +3231,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -3222,7 +3246,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -3233,7 +3257,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -3244,7 +3268,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -3255,7 +3279,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -3266,7 +3290,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -3277,7 +3301,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -3288,7 +3312,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -3299,7 +3323,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -3310,7 +3334,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -3321,7 +3345,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -3332,7 +3356,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -3343,7 +3367,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -3354,7 +3378,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -3362,7 +3386,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -3370,7 +3394,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -3378,7 +3402,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -3386,7 +3410,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -3394,7 +3418,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -3402,7 +3426,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -3410,7 +3434,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -3418,7 +3442,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3426,7 +3450,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3434,236 +3458,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3685,27 +3714,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3725,122 +3754,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3864,456 +3893,456 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
     </row>
     <row r="2" spans="1:76" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
     </row>
   </sheetData>
@@ -4364,181 +4393,181 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:BV289"/>
+  <dimension ref="G1:BV294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:74">
       <c r="G1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Z1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AD1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AE1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AF1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AG1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AL1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AY1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="BB1" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="BI1" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="BS1" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="BU1" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="BV1" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
     </row>
     <row r="2" spans="7:74">
       <c r="G2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Z2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AD2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AE2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AF2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AG2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AY2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="BB2" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="BI2" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="BS2" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="BU2" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="BV2" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
     </row>
     <row r="3" spans="7:74">
       <c r="G3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AD3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AE3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AF3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AL3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AY3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="BB3" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="BI3" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="BU3" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="BV3" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
     </row>
     <row r="4" spans="7:74">
       <c r="G4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AD4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AE4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AY4" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="BB4" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="BI4" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="BU4" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="BV4" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
     </row>
     <row r="5" spans="7:74">
       <c r="G5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AD5" t="s">
         <v>116</v>
       </c>
       <c r="AE5" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AY5" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="BB5" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="BU5" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="BV5" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
     </row>
     <row r="6" spans="7:74">
       <c r="AD6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AE6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AY6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="BB6" t="s">
         <v>116</v>
@@ -4547,49 +4576,49 @@
         <v>116</v>
       </c>
       <c r="BV6" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
     </row>
     <row r="7" spans="7:74">
       <c r="AD7" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AE7" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AY7" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="BB7" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="BV7" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
     </row>
     <row r="8" spans="7:74">
       <c r="AD8" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AE8" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AY8" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="BV8" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
     </row>
     <row r="9" spans="7:74">
       <c r="AD9" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AE9" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AY9" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="BV9" t="s">
         <v>116</v>
@@ -4597,1417 +4626,1442 @@
     </row>
     <row r="10" spans="7:74">
       <c r="AD10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AE10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AY10" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="BV10" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
     </row>
     <row r="11" spans="7:74">
       <c r="AY11" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="BV11" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
     </row>
     <row r="12" spans="7:74">
       <c r="AY12" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="BV12" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
     </row>
     <row r="13" spans="7:74">
       <c r="AY13" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="14" spans="7:74">
       <c r="AY14" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="15" spans="7:74">
       <c r="AY15" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="16" spans="7:74">
       <c r="AY16" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="17" spans="51:51">
       <c r="AY17" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="18" spans="51:51">
       <c r="AY18" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="19" spans="51:51">
       <c r="AY19" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="20" spans="51:51">
       <c r="AY20" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="21" spans="51:51">
       <c r="AY21" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="22" spans="51:51">
       <c r="AY22" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="23" spans="51:51">
       <c r="AY23" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="24" spans="51:51">
       <c r="AY24" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="25" spans="51:51">
       <c r="AY25" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="26" spans="51:51">
       <c r="AY26" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="27" spans="51:51">
       <c r="AY27" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="28" spans="51:51">
       <c r="AY28" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="29" spans="51:51">
       <c r="AY29" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="30" spans="51:51">
       <c r="AY30" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="31" spans="51:51">
       <c r="AY31" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="32" spans="51:51">
       <c r="AY32" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="33" spans="51:51">
       <c r="AY33" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="34" spans="51:51">
       <c r="AY34" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="35" spans="51:51">
       <c r="AY35" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="36" spans="51:51">
       <c r="AY36" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="37" spans="51:51">
       <c r="AY37" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="38" spans="51:51">
       <c r="AY38" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="39" spans="51:51">
       <c r="AY39" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="40" spans="51:51">
       <c r="AY40" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="41" spans="51:51">
       <c r="AY41" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="42" spans="51:51">
       <c r="AY42" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="43" spans="51:51">
       <c r="AY43" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="44" spans="51:51">
       <c r="AY44" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="45" spans="51:51">
       <c r="AY45" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="46" spans="51:51">
       <c r="AY46" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="47" spans="51:51">
       <c r="AY47" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="48" spans="51:51">
       <c r="AY48" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="49" spans="51:51">
       <c r="AY49" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="50" spans="51:51">
       <c r="AY50" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="51" spans="51:51">
       <c r="AY51" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="52" spans="51:51">
       <c r="AY52" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="53" spans="51:51">
       <c r="AY53" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="54" spans="51:51">
       <c r="AY54" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="55" spans="51:51">
       <c r="AY55" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="56" spans="51:51">
       <c r="AY56" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="57" spans="51:51">
       <c r="AY57" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="58" spans="51:51">
       <c r="AY58" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="59" spans="51:51">
       <c r="AY59" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="60" spans="51:51">
       <c r="AY60" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="61" spans="51:51">
       <c r="AY61" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="62" spans="51:51">
       <c r="AY62" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="63" spans="51:51">
       <c r="AY63" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="64" spans="51:51">
       <c r="AY64" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="65" spans="51:51">
       <c r="AY65" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="66" spans="51:51">
       <c r="AY66" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="67" spans="51:51">
       <c r="AY67" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="68" spans="51:51">
       <c r="AY68" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="69" spans="51:51">
       <c r="AY69" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="70" spans="51:51">
       <c r="AY70" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="71" spans="51:51">
       <c r="AY71" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="72" spans="51:51">
       <c r="AY72" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="73" spans="51:51">
       <c r="AY73" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="74" spans="51:51">
       <c r="AY74" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="75" spans="51:51">
       <c r="AY75" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="76" spans="51:51">
       <c r="AY76" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="77" spans="51:51">
       <c r="AY77" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="78" spans="51:51">
       <c r="AY78" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="79" spans="51:51">
       <c r="AY79" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="80" spans="51:51">
       <c r="AY80" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="81" spans="51:51">
       <c r="AY81" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="82" spans="51:51">
       <c r="AY82" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="83" spans="51:51">
       <c r="AY83" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="84" spans="51:51">
       <c r="AY84" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="85" spans="51:51">
       <c r="AY85" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="86" spans="51:51">
       <c r="AY86" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="87" spans="51:51">
       <c r="AY87" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="88" spans="51:51">
       <c r="AY88" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="89" spans="51:51">
       <c r="AY89" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="90" spans="51:51">
       <c r="AY90" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="91" spans="51:51">
       <c r="AY91" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="92" spans="51:51">
       <c r="AY92" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="93" spans="51:51">
       <c r="AY93" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="94" spans="51:51">
       <c r="AY94" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="95" spans="51:51">
       <c r="AY95" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="96" spans="51:51">
       <c r="AY96" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="97" spans="51:51">
       <c r="AY97" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="98" spans="51:51">
       <c r="AY98" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="99" spans="51:51">
       <c r="AY99" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="100" spans="51:51">
       <c r="AY100" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="101" spans="51:51">
       <c r="AY101" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="102" spans="51:51">
       <c r="AY102" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="103" spans="51:51">
       <c r="AY103" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="104" spans="51:51">
       <c r="AY104" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="105" spans="51:51">
       <c r="AY105" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="106" spans="51:51">
       <c r="AY106" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="107" spans="51:51">
       <c r="AY107" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="108" spans="51:51">
       <c r="AY108" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="109" spans="51:51">
       <c r="AY109" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="110" spans="51:51">
       <c r="AY110" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="111" spans="51:51">
       <c r="AY111" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="112" spans="51:51">
       <c r="AY112" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="113" spans="51:51">
       <c r="AY113" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="114" spans="51:51">
       <c r="AY114" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="115" spans="51:51">
       <c r="AY115" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="116" spans="51:51">
       <c r="AY116" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="117" spans="51:51">
       <c r="AY117" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="118" spans="51:51">
       <c r="AY118" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="119" spans="51:51">
       <c r="AY119" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="120" spans="51:51">
       <c r="AY120" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="121" spans="51:51">
       <c r="AY121" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="122" spans="51:51">
       <c r="AY122" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="123" spans="51:51">
       <c r="AY123" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="124" spans="51:51">
       <c r="AY124" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="125" spans="51:51">
       <c r="AY125" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="126" spans="51:51">
       <c r="AY126" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="127" spans="51:51">
       <c r="AY127" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="128" spans="51:51">
       <c r="AY128" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="129" spans="51:51">
       <c r="AY129" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="130" spans="51:51">
       <c r="AY130" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="131" spans="51:51">
       <c r="AY131" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="132" spans="51:51">
       <c r="AY132" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="133" spans="51:51">
       <c r="AY133" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="134" spans="51:51">
       <c r="AY134" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="135" spans="51:51">
       <c r="AY135" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="136" spans="51:51">
       <c r="AY136" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="137" spans="51:51">
       <c r="AY137" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="138" spans="51:51">
       <c r="AY138" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="139" spans="51:51">
       <c r="AY139" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="140" spans="51:51">
       <c r="AY140" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="141" spans="51:51">
       <c r="AY141" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="142" spans="51:51">
       <c r="AY142" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="143" spans="51:51">
       <c r="AY143" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="144" spans="51:51">
       <c r="AY144" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="145" spans="51:51">
       <c r="AY145" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="146" spans="51:51">
       <c r="AY146" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="147" spans="51:51">
       <c r="AY147" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="148" spans="51:51">
       <c r="AY148" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="149" spans="51:51">
       <c r="AY149" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="150" spans="51:51">
       <c r="AY150" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="151" spans="51:51">
       <c r="AY151" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="152" spans="51:51">
       <c r="AY152" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="153" spans="51:51">
       <c r="AY153" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="154" spans="51:51">
       <c r="AY154" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="155" spans="51:51">
       <c r="AY155" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="156" spans="51:51">
       <c r="AY156" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="157" spans="51:51">
       <c r="AY157" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="158" spans="51:51">
       <c r="AY158" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="159" spans="51:51">
       <c r="AY159" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="160" spans="51:51">
       <c r="AY160" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="161" spans="51:51">
       <c r="AY161" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="162" spans="51:51">
       <c r="AY162" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="163" spans="51:51">
       <c r="AY163" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="164" spans="51:51">
       <c r="AY164" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="165" spans="51:51">
       <c r="AY165" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="166" spans="51:51">
       <c r="AY166" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="167" spans="51:51">
       <c r="AY167" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="168" spans="51:51">
       <c r="AY168" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="169" spans="51:51">
       <c r="AY169" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="170" spans="51:51">
       <c r="AY170" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="171" spans="51:51">
       <c r="AY171" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="172" spans="51:51">
       <c r="AY172" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="173" spans="51:51">
       <c r="AY173" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="174" spans="51:51">
       <c r="AY174" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="175" spans="51:51">
       <c r="AY175" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="176" spans="51:51">
       <c r="AY176" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="177" spans="51:51">
       <c r="AY177" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="178" spans="51:51">
       <c r="AY178" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="179" spans="51:51">
       <c r="AY179" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="180" spans="51:51">
       <c r="AY180" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="181" spans="51:51">
       <c r="AY181" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="182" spans="51:51">
       <c r="AY182" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="183" spans="51:51">
       <c r="AY183" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="184" spans="51:51">
       <c r="AY184" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="185" spans="51:51">
       <c r="AY185" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="186" spans="51:51">
       <c r="AY186" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="187" spans="51:51">
       <c r="AY187" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="188" spans="51:51">
       <c r="AY188" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="189" spans="51:51">
       <c r="AY189" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="190" spans="51:51">
       <c r="AY190" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="191" spans="51:51">
       <c r="AY191" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="192" spans="51:51">
       <c r="AY192" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="193" spans="51:51">
       <c r="AY193" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="194" spans="51:51">
       <c r="AY194" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="195" spans="51:51">
       <c r="AY195" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="196" spans="51:51">
       <c r="AY196" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="197" spans="51:51">
       <c r="AY197" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="198" spans="51:51">
       <c r="AY198" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="199" spans="51:51">
       <c r="AY199" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="200" spans="51:51">
       <c r="AY200" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="201" spans="51:51">
       <c r="AY201" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="202" spans="51:51">
       <c r="AY202" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="203" spans="51:51">
       <c r="AY203" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="204" spans="51:51">
       <c r="AY204" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="205" spans="51:51">
       <c r="AY205" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="206" spans="51:51">
       <c r="AY206" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="207" spans="51:51">
       <c r="AY207" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="208" spans="51:51">
       <c r="AY208" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="209" spans="51:51">
       <c r="AY209" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="210" spans="51:51">
       <c r="AY210" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="211" spans="51:51">
       <c r="AY211" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="212" spans="51:51">
       <c r="AY212" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="213" spans="51:51">
       <c r="AY213" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="214" spans="51:51">
       <c r="AY214" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="215" spans="51:51">
       <c r="AY215" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="216" spans="51:51">
       <c r="AY216" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="217" spans="51:51">
       <c r="AY217" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="218" spans="51:51">
       <c r="AY218" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="219" spans="51:51">
       <c r="AY219" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="220" spans="51:51">
       <c r="AY220" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="221" spans="51:51">
       <c r="AY221" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="222" spans="51:51">
       <c r="AY222" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="223" spans="51:51">
       <c r="AY223" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="224" spans="51:51">
       <c r="AY224" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="225" spans="51:51">
       <c r="AY225" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="226" spans="51:51">
       <c r="AY226" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="227" spans="51:51">
       <c r="AY227" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="228" spans="51:51">
       <c r="AY228" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="229" spans="51:51">
       <c r="AY229" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="230" spans="51:51">
       <c r="AY230" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="231" spans="51:51">
       <c r="AY231" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="232" spans="51:51">
       <c r="AY232" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="233" spans="51:51">
       <c r="AY233" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="234" spans="51:51">
       <c r="AY234" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="235" spans="51:51">
       <c r="AY235" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="236" spans="51:51">
       <c r="AY236" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="237" spans="51:51">
       <c r="AY237" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="238" spans="51:51">
       <c r="AY238" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="239" spans="51:51">
       <c r="AY239" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="240" spans="51:51">
       <c r="AY240" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="241" spans="51:51">
       <c r="AY241" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="242" spans="51:51">
       <c r="AY242" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="243" spans="51:51">
       <c r="AY243" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="244" spans="51:51">
       <c r="AY244" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="245" spans="51:51">
       <c r="AY245" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="246" spans="51:51">
       <c r="AY246" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="247" spans="51:51">
       <c r="AY247" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="248" spans="51:51">
       <c r="AY248" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="249" spans="51:51">
       <c r="AY249" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="250" spans="51:51">
       <c r="AY250" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="251" spans="51:51">
       <c r="AY251" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="252" spans="51:51">
       <c r="AY252" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="253" spans="51:51">
       <c r="AY253" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="254" spans="51:51">
       <c r="AY254" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="255" spans="51:51">
       <c r="AY255" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="256" spans="51:51">
       <c r="AY256" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="257" spans="51:51">
       <c r="AY257" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="258" spans="51:51">
       <c r="AY258" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="259" spans="51:51">
       <c r="AY259" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="260" spans="51:51">
       <c r="AY260" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="261" spans="51:51">
       <c r="AY261" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="262" spans="51:51">
       <c r="AY262" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="263" spans="51:51">
       <c r="AY263" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="264" spans="51:51">
       <c r="AY264" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="265" spans="51:51">
       <c r="AY265" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="266" spans="51:51">
       <c r="AY266" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="267" spans="51:51">
       <c r="AY267" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="268" spans="51:51">
       <c r="AY268" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="269" spans="51:51">
       <c r="AY269" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="270" spans="51:51">
       <c r="AY270" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="271" spans="51:51">
       <c r="AY271" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="272" spans="51:51">
       <c r="AY272" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="273" spans="51:51">
       <c r="AY273" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="274" spans="51:51">
       <c r="AY274" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="275" spans="51:51">
       <c r="AY275" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="276" spans="51:51">
       <c r="AY276" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="277" spans="51:51">
       <c r="AY277" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="278" spans="51:51">
       <c r="AY278" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="279" spans="51:51">
       <c r="AY279" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="280" spans="51:51">
       <c r="AY280" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="281" spans="51:51">
       <c r="AY281" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="282" spans="51:51">
       <c r="AY282" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="283" spans="51:51">
       <c r="AY283" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="284" spans="51:51">
       <c r="AY284" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="285" spans="51:51">
       <c r="AY285" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="286" spans="51:51">
       <c r="AY286" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="287" spans="51:51">
       <c r="AY287" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="288" spans="51:51">
       <c r="AY288" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="289" spans="51:51">
       <c r="AY289" t="s">
-        <v>684</v>
+        <v>686</v>
+      </c>
+    </row>
+    <row r="290" spans="51:51">
+      <c r="AY290" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="291" spans="51:51">
+      <c r="AY291" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="292" spans="51:51">
+      <c r="AY292" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="293" spans="51:51">
+      <c r="AY293" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="294" spans="51:51">
+      <c r="AY294" t="s">
+        <v>691</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000049/metadata_template_ERC000049.xlsx
+++ b/templates/ERC000049/metadata_template_ERC000049.xlsx
@@ -21,7 +21,7 @@
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AY$1:$AY$294</definedName>
     <definedName name="hostpredictionapproach">'cv_sample'!$BB$1:$BB$7</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$89</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="772">
   <si>
     <t>alias</t>
   </si>
@@ -739,6 +739,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>UG 200</t>
   </si>
   <si>
     <t>Vega</t>
@@ -2885,7 +2888,7 @@
         <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2929,7 +2932,7 @@
         <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -2956,7 +2959,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N88"/>
+  <dimension ref="G1:N89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3693,6 +3696,11 @@
     </row>
     <row r="88" spans="14:14">
       <c r="N88" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="89" spans="14:14">
+      <c r="N89" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3714,27 +3722,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -3754,122 +3762,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -3893,456 +3901,456 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="2" spans="1:76" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
   </sheetData>
@@ -4398,176 +4406,176 @@
   <sheetData>
     <row r="1" spans="7:74">
       <c r="G1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Z1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AD1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AE1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AF1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AY1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="BB1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="BI1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="BS1" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="BU1" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="BV1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="2" spans="7:74">
       <c r="G2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Z2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AD2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AE2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AF2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AL2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AY2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="BB2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="BI2" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="BS2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="BU2" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="BV2" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="3" spans="7:74">
       <c r="G3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AD3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AE3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AF3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AY3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="BB3" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="BI3" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="BU3" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="BV3" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="4" spans="7:74">
       <c r="G4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AD4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AE4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AY4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="BB4" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="BI4" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="BU4" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="BV4" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="5" spans="7:74">
       <c r="G5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AD5" t="s">
         <v>116</v>
       </c>
       <c r="AE5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AY5" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="BB5" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="BU5" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="BV5" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="6" spans="7:74">
       <c r="AD6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AE6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AY6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="BB6" t="s">
         <v>116</v>
@@ -4576,49 +4584,49 @@
         <v>116</v>
       </c>
       <c r="BV6" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="7" spans="7:74">
       <c r="AD7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AE7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AY7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="BB7" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="BV7" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="8" spans="7:74">
       <c r="AD8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AE8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AY8" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="BV8" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="9" spans="7:74">
       <c r="AD9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AE9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AY9" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="BV9" t="s">
         <v>116</v>
@@ -4626,1442 +4634,1442 @@
     </row>
     <row r="10" spans="7:74">
       <c r="AD10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AE10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AY10" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="BV10" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="11" spans="7:74">
       <c r="AY11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="BV11" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="12" spans="7:74">
       <c r="AY12" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="BV12" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="13" spans="7:74">
       <c r="AY13" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="14" spans="7:74">
       <c r="AY14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="15" spans="7:74">
       <c r="AY15" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="16" spans="7:74">
       <c r="AY16" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="17" spans="51:51">
       <c r="AY17" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="18" spans="51:51">
       <c r="AY18" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="19" spans="51:51">
       <c r="AY19" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="20" spans="51:51">
       <c r="AY20" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="21" spans="51:51">
       <c r="AY21" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="22" spans="51:51">
       <c r="AY22" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="23" spans="51:51">
       <c r="AY23" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="24" spans="51:51">
       <c r="AY24" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="25" spans="51:51">
       <c r="AY25" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="26" spans="51:51">
       <c r="AY26" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="27" spans="51:51">
       <c r="AY27" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="28" spans="51:51">
       <c r="AY28" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="29" spans="51:51">
       <c r="AY29" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="30" spans="51:51">
       <c r="AY30" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="31" spans="51:51">
       <c r="AY31" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="32" spans="51:51">
       <c r="AY32" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="33" spans="51:51">
       <c r="AY33" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="34" spans="51:51">
       <c r="AY34" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="35" spans="51:51">
       <c r="AY35" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="36" spans="51:51">
       <c r="AY36" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="37" spans="51:51">
       <c r="AY37" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="38" spans="51:51">
       <c r="AY38" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="39" spans="51:51">
       <c r="AY39" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="40" spans="51:51">
       <c r="AY40" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="41" spans="51:51">
       <c r="AY41" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="42" spans="51:51">
       <c r="AY42" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="43" spans="51:51">
       <c r="AY43" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="44" spans="51:51">
       <c r="AY44" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="45" spans="51:51">
       <c r="AY45" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="46" spans="51:51">
       <c r="AY46" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="47" spans="51:51">
       <c r="AY47" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="48" spans="51:51">
       <c r="AY48" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="49" spans="51:51">
       <c r="AY49" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="50" spans="51:51">
       <c r="AY50" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="51" spans="51:51">
       <c r="AY51" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="52" spans="51:51">
       <c r="AY52" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="53" spans="51:51">
       <c r="AY53" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="54" spans="51:51">
       <c r="AY54" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="55" spans="51:51">
       <c r="AY55" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="56" spans="51:51">
       <c r="AY56" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="57" spans="51:51">
       <c r="AY57" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="58" spans="51:51">
       <c r="AY58" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="59" spans="51:51">
       <c r="AY59" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="60" spans="51:51">
       <c r="AY60" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="61" spans="51:51">
       <c r="AY61" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="62" spans="51:51">
       <c r="AY62" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="63" spans="51:51">
       <c r="AY63" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="64" spans="51:51">
       <c r="AY64" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="65" spans="51:51">
       <c r="AY65" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="66" spans="51:51">
       <c r="AY66" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="67" spans="51:51">
       <c r="AY67" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="68" spans="51:51">
       <c r="AY68" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="69" spans="51:51">
       <c r="AY69" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="70" spans="51:51">
       <c r="AY70" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="71" spans="51:51">
       <c r="AY71" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="72" spans="51:51">
       <c r="AY72" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="73" spans="51:51">
       <c r="AY73" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="74" spans="51:51">
       <c r="AY74" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="75" spans="51:51">
       <c r="AY75" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="76" spans="51:51">
       <c r="AY76" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="77" spans="51:51">
       <c r="AY77" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="78" spans="51:51">
       <c r="AY78" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="79" spans="51:51">
       <c r="AY79" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="80" spans="51:51">
       <c r="AY80" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="81" spans="51:51">
       <c r="AY81" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="82" spans="51:51">
       <c r="AY82" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="83" spans="51:51">
       <c r="AY83" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="84" spans="51:51">
       <c r="AY84" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="85" spans="51:51">
       <c r="AY85" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="86" spans="51:51">
       <c r="AY86" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="87" spans="51:51">
       <c r="AY87" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="88" spans="51:51">
       <c r="AY88" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="89" spans="51:51">
       <c r="AY89" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="90" spans="51:51">
       <c r="AY90" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="91" spans="51:51">
       <c r="AY91" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="92" spans="51:51">
       <c r="AY92" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="93" spans="51:51">
       <c r="AY93" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="94" spans="51:51">
       <c r="AY94" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="95" spans="51:51">
       <c r="AY95" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="96" spans="51:51">
       <c r="AY96" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="97" spans="51:51">
       <c r="AY97" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="98" spans="51:51">
       <c r="AY98" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="99" spans="51:51">
       <c r="AY99" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="100" spans="51:51">
       <c r="AY100" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="101" spans="51:51">
       <c r="AY101" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="102" spans="51:51">
       <c r="AY102" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="103" spans="51:51">
       <c r="AY103" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="104" spans="51:51">
       <c r="AY104" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="105" spans="51:51">
       <c r="AY105" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="106" spans="51:51">
       <c r="AY106" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="107" spans="51:51">
       <c r="AY107" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="108" spans="51:51">
       <c r="AY108" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="109" spans="51:51">
       <c r="AY109" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="110" spans="51:51">
       <c r="AY110" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="111" spans="51:51">
       <c r="AY111" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="112" spans="51:51">
       <c r="AY112" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="113" spans="51:51">
       <c r="AY113" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="114" spans="51:51">
       <c r="AY114" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="115" spans="51:51">
       <c r="AY115" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="116" spans="51:51">
       <c r="AY116" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="117" spans="51:51">
       <c r="AY117" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="118" spans="51:51">
       <c r="AY118" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="119" spans="51:51">
       <c r="AY119" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="120" spans="51:51">
       <c r="AY120" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="121" spans="51:51">
       <c r="AY121" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="122" spans="51:51">
       <c r="AY122" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="123" spans="51:51">
       <c r="AY123" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="124" spans="51:51">
       <c r="AY124" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="125" spans="51:51">
       <c r="AY125" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="126" spans="51:51">
       <c r="AY126" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="127" spans="51:51">
       <c r="AY127" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="128" spans="51:51">
       <c r="AY128" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="129" spans="51:51">
       <c r="AY129" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="130" spans="51:51">
       <c r="AY130" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="131" spans="51:51">
       <c r="AY131" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="132" spans="51:51">
       <c r="AY132" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="133" spans="51:51">
       <c r="AY133" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="134" spans="51:51">
       <c r="AY134" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="135" spans="51:51">
       <c r="AY135" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="136" spans="51:51">
       <c r="AY136" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="137" spans="51:51">
       <c r="AY137" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="138" spans="51:51">
       <c r="AY138" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="139" spans="51:51">
       <c r="AY139" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="140" spans="51:51">
       <c r="AY140" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="141" spans="51:51">
       <c r="AY141" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="142" spans="51:51">
       <c r="AY142" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="143" spans="51:51">
       <c r="AY143" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="144" spans="51:51">
       <c r="AY144" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="145" spans="51:51">
       <c r="AY145" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="146" spans="51:51">
       <c r="AY146" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="147" spans="51:51">
       <c r="AY147" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="148" spans="51:51">
       <c r="AY148" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="149" spans="51:51">
       <c r="AY149" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="150" spans="51:51">
       <c r="AY150" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="151" spans="51:51">
       <c r="AY151" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="152" spans="51:51">
       <c r="AY152" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="153" spans="51:51">
       <c r="AY153" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="154" spans="51:51">
       <c r="AY154" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="155" spans="51:51">
       <c r="AY155" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="156" spans="51:51">
       <c r="AY156" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="157" spans="51:51">
       <c r="AY157" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="158" spans="51:51">
       <c r="AY158" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="159" spans="51:51">
       <c r="AY159" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="160" spans="51:51">
       <c r="AY160" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="161" spans="51:51">
       <c r="AY161" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="162" spans="51:51">
       <c r="AY162" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="163" spans="51:51">
       <c r="AY163" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="164" spans="51:51">
       <c r="AY164" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="165" spans="51:51">
       <c r="AY165" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="166" spans="51:51">
       <c r="AY166" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="167" spans="51:51">
       <c r="AY167" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="168" spans="51:51">
       <c r="AY168" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="169" spans="51:51">
       <c r="AY169" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="170" spans="51:51">
       <c r="AY170" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="171" spans="51:51">
       <c r="AY171" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="172" spans="51:51">
       <c r="AY172" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="173" spans="51:51">
       <c r="AY173" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="174" spans="51:51">
       <c r="AY174" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="175" spans="51:51">
       <c r="AY175" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="176" spans="51:51">
       <c r="AY176" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="177" spans="51:51">
       <c r="AY177" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="178" spans="51:51">
       <c r="AY178" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="179" spans="51:51">
       <c r="AY179" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="180" spans="51:51">
       <c r="AY180" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="181" spans="51:51">
       <c r="AY181" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="182" spans="51:51">
       <c r="AY182" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="183" spans="51:51">
       <c r="AY183" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="184" spans="51:51">
       <c r="AY184" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="185" spans="51:51">
       <c r="AY185" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="186" spans="51:51">
       <c r="AY186" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="187" spans="51:51">
       <c r="AY187" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="188" spans="51:51">
       <c r="AY188" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="189" spans="51:51">
       <c r="AY189" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="190" spans="51:51">
       <c r="AY190" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="191" spans="51:51">
       <c r="AY191" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="192" spans="51:51">
       <c r="AY192" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="193" spans="51:51">
       <c r="AY193" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="194" spans="51:51">
       <c r="AY194" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="195" spans="51:51">
       <c r="AY195" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="196" spans="51:51">
       <c r="AY196" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="197" spans="51:51">
       <c r="AY197" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="198" spans="51:51">
       <c r="AY198" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="199" spans="51:51">
       <c r="AY199" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="200" spans="51:51">
       <c r="AY200" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="201" spans="51:51">
       <c r="AY201" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="202" spans="51:51">
       <c r="AY202" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="203" spans="51:51">
       <c r="AY203" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="204" spans="51:51">
       <c r="AY204" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="205" spans="51:51">
       <c r="AY205" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="206" spans="51:51">
       <c r="AY206" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="207" spans="51:51">
       <c r="AY207" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="208" spans="51:51">
       <c r="AY208" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="209" spans="51:51">
       <c r="AY209" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="210" spans="51:51">
       <c r="AY210" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="211" spans="51:51">
       <c r="AY211" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="212" spans="51:51">
       <c r="AY212" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="213" spans="51:51">
       <c r="AY213" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="214" spans="51:51">
       <c r="AY214" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="215" spans="51:51">
       <c r="AY215" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="216" spans="51:51">
       <c r="AY216" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="217" spans="51:51">
       <c r="AY217" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="218" spans="51:51">
       <c r="AY218" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="219" spans="51:51">
       <c r="AY219" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="220" spans="51:51">
       <c r="AY220" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="221" spans="51:51">
       <c r="AY221" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="222" spans="51:51">
       <c r="AY222" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="223" spans="51:51">
       <c r="AY223" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="224" spans="51:51">
       <c r="AY224" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="225" spans="51:51">
       <c r="AY225" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="226" spans="51:51">
       <c r="AY226" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="227" spans="51:51">
       <c r="AY227" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="228" spans="51:51">
       <c r="AY228" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="229" spans="51:51">
       <c r="AY229" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="230" spans="51:51">
       <c r="AY230" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="231" spans="51:51">
       <c r="AY231" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="232" spans="51:51">
       <c r="AY232" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="233" spans="51:51">
       <c r="AY233" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="234" spans="51:51">
       <c r="AY234" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="235" spans="51:51">
       <c r="AY235" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="236" spans="51:51">
       <c r="AY236" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="237" spans="51:51">
       <c r="AY237" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="238" spans="51:51">
       <c r="AY238" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="239" spans="51:51">
       <c r="AY239" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="240" spans="51:51">
       <c r="AY240" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="241" spans="51:51">
       <c r="AY241" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="242" spans="51:51">
       <c r="AY242" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="243" spans="51:51">
       <c r="AY243" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="244" spans="51:51">
       <c r="AY244" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="245" spans="51:51">
       <c r="AY245" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="246" spans="51:51">
       <c r="AY246" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="247" spans="51:51">
       <c r="AY247" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="248" spans="51:51">
       <c r="AY248" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="249" spans="51:51">
       <c r="AY249" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="250" spans="51:51">
       <c r="AY250" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="251" spans="51:51">
       <c r="AY251" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="252" spans="51:51">
       <c r="AY252" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="253" spans="51:51">
       <c r="AY253" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="254" spans="51:51">
       <c r="AY254" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="255" spans="51:51">
       <c r="AY255" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="256" spans="51:51">
       <c r="AY256" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="257" spans="51:51">
       <c r="AY257" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="258" spans="51:51">
       <c r="AY258" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="259" spans="51:51">
       <c r="AY259" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="260" spans="51:51">
       <c r="AY260" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="261" spans="51:51">
       <c r="AY261" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="262" spans="51:51">
       <c r="AY262" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="263" spans="51:51">
       <c r="AY263" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="264" spans="51:51">
       <c r="AY264" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="265" spans="51:51">
       <c r="AY265" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="266" spans="51:51">
       <c r="AY266" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="267" spans="51:51">
       <c r="AY267" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="268" spans="51:51">
       <c r="AY268" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="269" spans="51:51">
       <c r="AY269" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="270" spans="51:51">
       <c r="AY270" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="271" spans="51:51">
       <c r="AY271" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="272" spans="51:51">
       <c r="AY272" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="273" spans="51:51">
       <c r="AY273" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="274" spans="51:51">
       <c r="AY274" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="275" spans="51:51">
       <c r="AY275" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="276" spans="51:51">
       <c r="AY276" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="277" spans="51:51">
       <c r="AY277" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="278" spans="51:51">
       <c r="AY278" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="279" spans="51:51">
       <c r="AY279" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="280" spans="51:51">
       <c r="AY280" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="281" spans="51:51">
       <c r="AY281" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="282" spans="51:51">
       <c r="AY282" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="283" spans="51:51">
       <c r="AY283" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="284" spans="51:51">
       <c r="AY284" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="285" spans="51:51">
       <c r="AY285" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="286" spans="51:51">
       <c r="AY286" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="287" spans="51:51">
       <c r="AY287" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="288" spans="51:51">
       <c r="AY288" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="289" spans="51:51">
       <c r="AY289" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="290" spans="51:51">
       <c r="AY290" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="291" spans="51:51">
       <c r="AY291" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="292" spans="51:51">
       <c r="AY292" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="293" spans="51:51">
       <c r="AY293" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="294" spans="51:51">
       <c r="AY294" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
   </sheetData>
